--- a/data/data_clean.xlsx
+++ b/data/data_clean.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>Ratio MeOH/Fa</t>
+          <t>Ratio Stab/Fa</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
@@ -783,14 +783,10 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="n">
         <v>5</v>
       </c>
@@ -935,12 +931,12 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM3" t="n">
@@ -1077,12 +1073,12 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM4" t="n">
@@ -1219,12 +1215,12 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM5" t="n">
@@ -1361,12 +1357,12 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM6" t="n">
@@ -1515,14 +1511,10 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="n">
         <v>2.5</v>
       </c>
@@ -1667,14 +1659,10 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="n">
         <v>2.5</v>
       </c>
@@ -1819,12 +1807,12 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM9" t="n">
@@ -1973,12 +1961,12 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM10" t="n">
@@ -2127,12 +2115,12 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM11" t="n">
@@ -2281,12 +2269,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM12" t="n">
@@ -2435,12 +2423,12 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM13" t="n">
@@ -2589,12 +2577,12 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM14" t="n">
@@ -2743,12 +2731,12 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM15" t="n">
@@ -2897,12 +2885,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM16" t="n">
@@ -3051,12 +3039,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM17" t="n">
@@ -3205,12 +3193,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM18" t="n">
@@ -3359,12 +3347,12 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM19" t="n">
@@ -3511,12 +3499,12 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM20" t="n">
@@ -3663,12 +3651,12 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM21" t="n">
@@ -3815,12 +3803,12 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM22" t="n">
@@ -3967,12 +3955,12 @@
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM23" t="n">
@@ -4119,12 +4107,12 @@
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM24" t="n">
@@ -4271,12 +4259,12 @@
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM25" t="n">
@@ -4423,12 +4411,12 @@
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM26" t="n">
@@ -4575,12 +4563,12 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM27" t="n">
@@ -4729,12 +4717,12 @@
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM28" t="n">
@@ -4883,12 +4871,12 @@
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM29" t="n">
@@ -5037,12 +5025,12 @@
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM30" t="n">
@@ -5191,14 +5179,10 @@
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL31" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr"/>
       <c r="AM31" t="n">
         <v>5</v>
       </c>
@@ -5335,14 +5319,10 @@
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr"/>
       <c r="AM32" t="n">
         <v>5</v>
       </c>
@@ -5487,14 +5467,10 @@
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL33" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr"/>
       <c r="AM33" t="n">
         <v>5</v>
       </c>
@@ -5639,14 +5615,10 @@
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL34" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL34" t="inlineStr"/>
       <c r="AM34" t="n">
         <v>5</v>
       </c>
@@ -5791,12 +5763,12 @@
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM35" t="n">
@@ -5943,12 +5915,12 @@
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM36" t="n">
@@ -6095,12 +6067,12 @@
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM37" t="n">
@@ -6247,12 +6219,12 @@
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM38" t="n">
@@ -6402,11 +6374,7 @@
           <t>DMM</t>
         </is>
       </c>
-      <c r="AL39" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="AL39" t="inlineStr"/>
       <c r="AM39" t="n">
         <v>0.5</v>
       </c>
@@ -6543,12 +6511,12 @@
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM40" t="n">
@@ -6697,12 +6665,12 @@
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL41" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM41" t="n">
@@ -6849,14 +6817,10 @@
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL42" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL42" t="inlineStr"/>
       <c r="AM42" t="n">
         <v>10</v>
       </c>
@@ -6991,14 +6955,10 @@
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL43" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL43" t="inlineStr"/>
       <c r="AM43" t="n">
         <v>3</v>
       </c>
@@ -7143,14 +7103,10 @@
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL44" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL44" t="inlineStr"/>
       <c r="AM44" t="n">
         <v>3</v>
       </c>
@@ -7295,14 +7251,10 @@
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL45" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL45" t="inlineStr"/>
       <c r="AM45" t="n">
         <v>3</v>
       </c>
@@ -7447,14 +7399,10 @@
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL46" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL46" t="inlineStr"/>
       <c r="AM46" t="n">
         <v>3</v>
       </c>
@@ -7599,12 +7547,12 @@
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL47" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM47" t="n">
@@ -7747,14 +7695,10 @@
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL48" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL48" t="inlineStr"/>
       <c r="AM48" t="n">
         <v>10</v>
       </c>
@@ -7889,12 +7833,12 @@
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL49" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM49" t="n">
@@ -8043,14 +7987,10 @@
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL50" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL50" t="inlineStr"/>
       <c r="AM50" t="n">
         <v>5</v>
       </c>
@@ -8195,14 +8135,10 @@
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL51" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL51" t="inlineStr"/>
       <c r="AM51" t="n">
         <v>5</v>
       </c>
@@ -8347,14 +8283,10 @@
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL52" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL52" t="inlineStr"/>
       <c r="AM52" t="n">
         <v>5</v>
       </c>
@@ -8499,12 +8431,12 @@
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL53" t="inlineStr">
         <is>
-          <t>Ethanol</t>
+          <t>EtOH</t>
         </is>
       </c>
       <c r="AM53" t="n">
@@ -8647,12 +8579,12 @@
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL54" t="inlineStr">
         <is>
-          <t>Ethanol</t>
+          <t>EtOH</t>
         </is>
       </c>
       <c r="AM54" t="n">
@@ -8795,12 +8727,12 @@
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL55" t="inlineStr">
         <is>
-          <t>Ethanol</t>
+          <t>EtOH</t>
         </is>
       </c>
       <c r="AM55" t="n">
@@ -8943,12 +8875,12 @@
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL56" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM56" t="n">
@@ -9097,12 +9029,12 @@
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL57" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM57" t="n">
@@ -9251,12 +9183,12 @@
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL58" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM58" t="n">
@@ -9405,12 +9337,12 @@
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Formalin</t>
+          <t>FORM</t>
         </is>
       </c>
       <c r="AL59" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM59" t="n">
@@ -9557,12 +9489,12 @@
       </c>
       <c r="AK60" t="inlineStr">
         <is>
-          <t>Formalin</t>
+          <t>FORM</t>
         </is>
       </c>
       <c r="AL60" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM60" t="n">
@@ -9709,12 +9641,12 @@
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Formalin</t>
+          <t>FORM</t>
         </is>
       </c>
       <c r="AL61" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM61" t="n">
@@ -9861,12 +9793,12 @@
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Formalin</t>
+          <t>FORM</t>
         </is>
       </c>
       <c r="AL62" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM62" t="n">
@@ -10013,12 +9945,12 @@
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL63" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM63" t="n">
@@ -10167,12 +10099,12 @@
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL64" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM64" t="n">
@@ -10321,12 +10253,12 @@
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL65" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM65" t="n">
@@ -10475,12 +10407,12 @@
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL66" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM66" t="n">
@@ -10629,12 +10561,12 @@
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL67" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM67" t="n">
@@ -10783,12 +10715,12 @@
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL68" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM68" t="n">
@@ -10937,12 +10869,12 @@
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL69" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM69" t="n">
@@ -11091,14 +11023,10 @@
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL70" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL70" t="inlineStr"/>
       <c r="AM70" t="n">
         <v>5</v>
       </c>
@@ -11243,14 +11171,10 @@
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL71" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL71" t="inlineStr"/>
       <c r="AM71" t="n">
         <v>5</v>
       </c>
@@ -11395,12 +11319,12 @@
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL72" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM72" t="n">
@@ -11539,12 +11463,12 @@
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL73" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM73" t="n">
@@ -11683,12 +11607,12 @@
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL74" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM74" t="n">
@@ -11827,14 +11751,10 @@
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL75" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL75" t="inlineStr"/>
       <c r="AM75" t="n">
         <v>0.5</v>
       </c>
@@ -11979,14 +11899,10 @@
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL76" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL76" t="inlineStr"/>
       <c r="AM76" t="n">
         <v>2</v>
       </c>
@@ -12131,12 +12047,12 @@
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL77" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM77" t="n">
@@ -12285,14 +12201,10 @@
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL78" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL78" t="inlineStr"/>
       <c r="AM78" t="n">
         <v>5</v>
       </c>
@@ -12437,14 +12349,10 @@
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL79" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL79" t="inlineStr"/>
       <c r="AM79" t="n">
         <v>5</v>
       </c>
@@ -12589,12 +12497,12 @@
       </c>
       <c r="AK80" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL80" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM80" t="n">
@@ -12733,12 +12641,12 @@
       </c>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL81" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM81" t="n">
@@ -12877,12 +12785,12 @@
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL82" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM82" t="n">
@@ -13031,12 +12939,12 @@
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL83" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM83" t="n">
@@ -13185,12 +13093,12 @@
       </c>
       <c r="AK84" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL84" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM84" t="n">
@@ -13339,12 +13247,12 @@
       </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL85" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM85" t="n">
@@ -13493,12 +13401,12 @@
       </c>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL86" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM86" t="n">
@@ -13647,12 +13555,12 @@
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL87" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM87" t="n">
@@ -13801,12 +13709,12 @@
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL88" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM88" t="n">
@@ -13955,12 +13863,12 @@
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL89" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM89" t="n">
@@ -14109,12 +14017,12 @@
       </c>
       <c r="AK90" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL90" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM90" t="n">
@@ -14263,12 +14171,12 @@
       </c>
       <c r="AK91" t="inlineStr">
         <is>
-          <t>Formalin</t>
+          <t>FORM</t>
         </is>
       </c>
       <c r="AL91" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM91" t="n">
@@ -14415,12 +14323,12 @@
       </c>
       <c r="AK92" t="inlineStr">
         <is>
-          <t>Formalin</t>
+          <t>FORM</t>
         </is>
       </c>
       <c r="AL92" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM92" t="n">
@@ -14567,12 +14475,12 @@
       </c>
       <c r="AK93" t="inlineStr">
         <is>
-          <t>Formalin</t>
+          <t>FORM</t>
         </is>
       </c>
       <c r="AL93" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM93" t="n">
@@ -14719,12 +14627,12 @@
       </c>
       <c r="AK94" t="inlineStr">
         <is>
-          <t>Formalin</t>
+          <t>FORM</t>
         </is>
       </c>
       <c r="AL94" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM94" t="n">
@@ -14871,12 +14779,12 @@
       </c>
       <c r="AK95" t="inlineStr">
         <is>
-          <t>Formalin</t>
+          <t>FORM</t>
         </is>
       </c>
       <c r="AL95" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM95" t="n">
@@ -15023,12 +14931,12 @@
       </c>
       <c r="AK96" t="inlineStr">
         <is>
-          <t>Formalin</t>
+          <t>FORM</t>
         </is>
       </c>
       <c r="AL96" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM96" t="n">
@@ -15175,12 +15083,12 @@
       </c>
       <c r="AK97" t="inlineStr">
         <is>
-          <t>Formalin</t>
+          <t>FORM</t>
         </is>
       </c>
       <c r="AL97" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM97" t="n">
@@ -15327,12 +15235,12 @@
       </c>
       <c r="AK98" t="inlineStr">
         <is>
-          <t>Formalin</t>
+          <t>FORM</t>
         </is>
       </c>
       <c r="AL98" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM98" t="n">
@@ -15479,12 +15387,12 @@
       </c>
       <c r="AK99" t="inlineStr">
         <is>
-          <t>Formalin</t>
+          <t>FORM</t>
         </is>
       </c>
       <c r="AL99" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM99" t="n">
@@ -15631,12 +15539,12 @@
       </c>
       <c r="AK100" t="inlineStr">
         <is>
-          <t>Formalin</t>
+          <t>FORM</t>
         </is>
       </c>
       <c r="AL100" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM100" t="n">
@@ -15783,12 +15691,12 @@
       </c>
       <c r="AK101" t="inlineStr">
         <is>
-          <t>Formalin</t>
+          <t>FORM</t>
         </is>
       </c>
       <c r="AL101" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM101" t="n">
@@ -15935,14 +15843,10 @@
       </c>
       <c r="AK102" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL102" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL102" t="inlineStr"/>
       <c r="AM102" t="n">
         <v>10</v>
       </c>
@@ -16077,14 +15981,10 @@
       </c>
       <c r="AK103" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL103" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL103" t="inlineStr"/>
       <c r="AM103" t="n">
         <v>10</v>
       </c>
@@ -16219,14 +16119,10 @@
       </c>
       <c r="AK104" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL104" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL104" t="inlineStr"/>
       <c r="AM104" t="n">
         <v>10</v>
       </c>
@@ -16361,14 +16257,10 @@
       </c>
       <c r="AK105" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL105" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL105" t="inlineStr"/>
       <c r="AM105" t="n">
         <v>10</v>
       </c>
@@ -16503,14 +16395,10 @@
       </c>
       <c r="AK106" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL106" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL106" t="inlineStr"/>
       <c r="AM106" t="n">
         <v>10</v>
       </c>
@@ -16645,14 +16533,10 @@
       </c>
       <c r="AK107" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL107" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL107" t="inlineStr"/>
       <c r="AM107" t="n">
         <v>10</v>
       </c>
@@ -16787,14 +16671,10 @@
       </c>
       <c r="AK108" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL108" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL108" t="inlineStr"/>
       <c r="AM108" t="n">
         <v>10</v>
       </c>
@@ -16929,14 +16809,10 @@
       </c>
       <c r="AK109" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL109" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL109" t="inlineStr"/>
       <c r="AM109" t="n">
         <v>10</v>
       </c>
@@ -17071,14 +16947,10 @@
       </c>
       <c r="AK110" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL110" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL110" t="inlineStr"/>
       <c r="AM110" t="n">
         <v>10</v>
       </c>
@@ -17213,14 +17085,10 @@
       </c>
       <c r="AK111" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL111" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL111" t="inlineStr"/>
       <c r="AM111" t="n">
         <v>10</v>
       </c>
@@ -17355,14 +17223,10 @@
       </c>
       <c r="AK112" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL112" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL112" t="inlineStr"/>
       <c r="AM112" t="n">
         <v>10</v>
       </c>
@@ -17497,14 +17361,10 @@
       </c>
       <c r="AK113" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL113" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL113" t="inlineStr"/>
       <c r="AM113" t="n">
         <v>5</v>
       </c>
@@ -17654,11 +17514,7 @@
           <t>DMM</t>
         </is>
       </c>
-      <c r="AL114" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="AL114" t="inlineStr"/>
       <c r="AM114" t="n">
         <v>0.5</v>
       </c>
@@ -17797,14 +17653,10 @@
       </c>
       <c r="AK115" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL115" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL115" t="inlineStr"/>
       <c r="AM115" t="n">
         <v>5</v>
       </c>
@@ -17954,11 +17806,7 @@
           <t>DMM</t>
         </is>
       </c>
-      <c r="AL116" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="AL116" t="inlineStr"/>
       <c r="AM116" t="n">
         <v>0.5</v>
       </c>
@@ -18100,11 +17948,7 @@
           <t>DMM</t>
         </is>
       </c>
-      <c r="AL117" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="AL117" t="inlineStr"/>
       <c r="AM117" t="n">
         <v>0.5</v>
       </c>
@@ -18243,14 +18087,10 @@
       </c>
       <c r="AK118" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL118" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL118" t="inlineStr"/>
       <c r="AM118" t="n">
         <v>5</v>
       </c>
@@ -18400,11 +18240,7 @@
           <t>DMM</t>
         </is>
       </c>
-      <c r="AL119" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="AL119" t="inlineStr"/>
       <c r="AM119" t="n">
         <v>0.5</v>
       </c>
@@ -18546,11 +18382,7 @@
           <t>DMM</t>
         </is>
       </c>
-      <c r="AL120" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="AL120" t="inlineStr"/>
       <c r="AM120" t="n">
         <v>2</v>
       </c>
@@ -18692,11 +18524,7 @@
           <t>DMM</t>
         </is>
       </c>
-      <c r="AL121" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="AL121" t="inlineStr"/>
       <c r="AM121" t="n">
         <v>0.5</v>
       </c>
@@ -18838,11 +18666,7 @@
           <t>DMM</t>
         </is>
       </c>
-      <c r="AL122" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="AL122" t="inlineStr"/>
       <c r="AM122" t="n">
         <v>0.5</v>
       </c>
@@ -18982,11 +18806,7 @@
           <t>DMM</t>
         </is>
       </c>
-      <c r="AL123" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="AL123" t="inlineStr"/>
       <c r="AM123" t="n">
         <v>0.5</v>
       </c>
@@ -19126,11 +18946,7 @@
           <t>DMM</t>
         </is>
       </c>
-      <c r="AL124" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="AL124" t="inlineStr"/>
       <c r="AM124" t="n">
         <v>0.5</v>
       </c>
@@ -19270,11 +19086,7 @@
           <t>DMM</t>
         </is>
       </c>
-      <c r="AL125" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="AL125" t="inlineStr"/>
       <c r="AM125" t="n">
         <v>0.5</v>
       </c>
@@ -19414,11 +19226,7 @@
           <t>DMM</t>
         </is>
       </c>
-      <c r="AL126" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="AL126" t="inlineStr"/>
       <c r="AM126" t="n">
         <v>0.5</v>
       </c>
@@ -19555,14 +19363,10 @@
       </c>
       <c r="AK127" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL127" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL127" t="inlineStr"/>
       <c r="AM127" t="n">
         <v>5</v>
       </c>
@@ -19707,14 +19511,10 @@
       </c>
       <c r="AK128" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL128" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL128" t="inlineStr"/>
       <c r="AM128" t="n">
         <v>5</v>
       </c>
@@ -19859,14 +19659,10 @@
       </c>
       <c r="AK129" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL129" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL129" t="inlineStr"/>
       <c r="AM129" t="n">
         <v>5</v>
       </c>
@@ -20011,14 +19807,10 @@
       </c>
       <c r="AK130" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL130" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL130" t="inlineStr"/>
       <c r="AM130" t="n">
         <v>5</v>
       </c>
@@ -20166,11 +19958,7 @@
           <t>DMM</t>
         </is>
       </c>
-      <c r="AL131" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="AL131" t="inlineStr"/>
       <c r="AM131" t="n">
         <v>0.5</v>
       </c>
@@ -20309,12 +20097,12 @@
       </c>
       <c r="AK132" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL132" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM132" t="n">
@@ -20453,12 +20241,12 @@
       </c>
       <c r="AK133" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL133" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM133" t="n">
@@ -20597,14 +20385,10 @@
       </c>
       <c r="AK134" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL134" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL134" t="inlineStr"/>
       <c r="AM134" t="n">
         <v>10</v>
       </c>
@@ -20739,14 +20523,10 @@
       </c>
       <c r="AK135" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL135" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL135" t="inlineStr"/>
       <c r="AM135" t="n">
         <v>2.5</v>
       </c>
@@ -20891,14 +20671,10 @@
       </c>
       <c r="AK136" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL136" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL136" t="inlineStr"/>
       <c r="AM136" t="n">
         <v>3</v>
       </c>
@@ -21043,12 +20819,12 @@
       </c>
       <c r="AK137" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL137" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM137" t="n">
@@ -21187,14 +20963,10 @@
       </c>
       <c r="AK138" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL138" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL138" t="inlineStr"/>
       <c r="AM138" t="n">
         <v>5</v>
       </c>
@@ -21339,14 +21111,10 @@
       </c>
       <c r="AK139" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL139" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL139" t="inlineStr"/>
       <c r="AM139" t="n">
         <v>2.5</v>
       </c>
@@ -21491,14 +21259,10 @@
       </c>
       <c r="AK140" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL140" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL140" t="inlineStr"/>
       <c r="AM140" t="n">
         <v>5</v>
       </c>
@@ -21643,14 +21407,10 @@
       </c>
       <c r="AK141" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL141" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL141" t="inlineStr"/>
       <c r="AM141" t="n">
         <v>5</v>
       </c>
@@ -21795,12 +21555,12 @@
       </c>
       <c r="AK142" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL142" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM142" t="n">
@@ -21939,14 +21699,10 @@
       </c>
       <c r="AK143" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL143" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL143" t="inlineStr"/>
       <c r="AM143" t="n">
         <v>5</v>
       </c>
@@ -22091,14 +21847,10 @@
       </c>
       <c r="AK144" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL144" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL144" t="inlineStr"/>
       <c r="AM144" t="n">
         <v>0.5</v>
       </c>
@@ -22243,12 +21995,12 @@
       </c>
       <c r="AK145" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL145" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM145" t="n">
@@ -22397,12 +22149,12 @@
       </c>
       <c r="AK146" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL146" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM146" t="n">
@@ -22551,14 +22303,10 @@
       </c>
       <c r="AK147" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL147" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL147" t="inlineStr"/>
       <c r="AM147" t="n">
         <v>10</v>
       </c>
@@ -22693,14 +22441,10 @@
       </c>
       <c r="AK148" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL148" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL148" t="inlineStr"/>
       <c r="AM148" t="n">
         <v>10</v>
       </c>
@@ -22835,14 +22579,10 @@
       </c>
       <c r="AK149" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL149" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL149" t="inlineStr"/>
       <c r="AM149" t="n">
         <v>10</v>
       </c>
@@ -22977,14 +22717,10 @@
       </c>
       <c r="AK150" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL150" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL150" t="inlineStr"/>
       <c r="AM150" t="n">
         <v>10</v>
       </c>
@@ -23119,14 +22855,10 @@
       </c>
       <c r="AK151" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL151" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL151" t="inlineStr"/>
       <c r="AM151" t="n">
         <v>10</v>
       </c>
@@ -23261,14 +22993,10 @@
       </c>
       <c r="AK152" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL152" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL152" t="inlineStr"/>
       <c r="AM152" t="n">
         <v>10</v>
       </c>
@@ -23403,14 +23131,10 @@
       </c>
       <c r="AK153" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL153" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL153" t="inlineStr"/>
       <c r="AM153" t="n">
         <v>10</v>
       </c>
@@ -23545,14 +23269,10 @@
       </c>
       <c r="AK154" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL154" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL154" t="inlineStr"/>
       <c r="AM154" t="n">
         <v>10</v>
       </c>
@@ -23687,14 +23407,10 @@
       </c>
       <c r="AK155" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL155" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL155" t="inlineStr"/>
       <c r="AM155" t="n">
         <v>10</v>
       </c>
@@ -23829,12 +23545,12 @@
       </c>
       <c r="AK156" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL156" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM156" t="n">
@@ -23973,12 +23689,12 @@
       </c>
       <c r="AK157" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL157" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM157" t="n">
@@ -24117,12 +23833,12 @@
       </c>
       <c r="AK158" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL158" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM158" t="n">
@@ -24261,12 +23977,12 @@
       </c>
       <c r="AK159" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL159" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM159" t="n">
@@ -24405,14 +24121,10 @@
       </c>
       <c r="AK160" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL160" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL160" t="inlineStr"/>
       <c r="AM160" t="n">
         <v>5</v>
       </c>
@@ -24557,12 +24269,12 @@
       </c>
       <c r="AK161" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL161" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM161" t="n">
@@ -24711,14 +24423,10 @@
       </c>
       <c r="AK162" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL162" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL162" t="inlineStr"/>
       <c r="AM162" t="n">
         <v>2.5</v>
       </c>
@@ -24863,12 +24571,12 @@
       </c>
       <c r="AK163" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL163" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM163" t="n">
@@ -25017,12 +24725,12 @@
       </c>
       <c r="AK164" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL164" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM164" t="n">
@@ -25171,14 +24879,10 @@
       </c>
       <c r="AK165" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL165" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL165" t="inlineStr"/>
       <c r="AM165" t="n">
         <v>5</v>
       </c>
@@ -25323,12 +25027,12 @@
       </c>
       <c r="AK166" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL166" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM166" t="n">
@@ -25477,12 +25181,12 @@
       </c>
       <c r="AK167" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL167" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM167" t="n">
@@ -25631,14 +25335,10 @@
       </c>
       <c r="AK168" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL168" t="inlineStr">
-        <is>
-          <t>Paraformaldehyde</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL168" t="inlineStr"/>
       <c r="AM168" t="n">
         <v>1</v>
       </c>
@@ -25775,14 +25475,10 @@
       </c>
       <c r="AK169" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL169" t="inlineStr">
-        <is>
-          <t>Paraformaldehyde</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL169" t="inlineStr"/>
       <c r="AM169" t="n">
         <v>1</v>
       </c>
@@ -25919,14 +25615,10 @@
       </c>
       <c r="AK170" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL170" t="inlineStr">
-        <is>
-          <t>Paraformaldehyde</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL170" t="inlineStr"/>
       <c r="AM170" t="n">
         <v>1</v>
       </c>
@@ -26063,14 +25755,10 @@
       </c>
       <c r="AK171" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL171" t="inlineStr">
-        <is>
-          <t>Paraformaldehyde</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL171" t="inlineStr"/>
       <c r="AM171" t="n">
         <v>1</v>
       </c>
@@ -26207,14 +25895,10 @@
       </c>
       <c r="AK172" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL172" t="inlineStr">
-        <is>
-          <t>Paraformaldehyde</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL172" t="inlineStr"/>
       <c r="AM172" t="n">
         <v>1</v>
       </c>
@@ -26351,14 +26035,10 @@
       </c>
       <c r="AK173" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL173" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL173" t="inlineStr"/>
       <c r="AM173" t="n">
         <v>0.2</v>
       </c>
@@ -26503,14 +26183,10 @@
       </c>
       <c r="AK174" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL174" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL174" t="inlineStr"/>
       <c r="AM174" t="n">
         <v>2.5</v>
       </c>
@@ -26655,14 +26331,10 @@
       </c>
       <c r="AK175" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL175" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL175" t="inlineStr"/>
       <c r="AM175" t="n">
         <v>0.4</v>
       </c>
@@ -26807,14 +26479,10 @@
       </c>
       <c r="AK176" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL176" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL176" t="inlineStr"/>
       <c r="AM176" t="n">
         <v>0.4</v>
       </c>
@@ -26961,14 +26629,10 @@
       </c>
       <c r="AK177" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL177" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL177" t="inlineStr"/>
       <c r="AM177" t="n">
         <v>0.4</v>
       </c>
@@ -27115,14 +26779,10 @@
       </c>
       <c r="AK178" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL178" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL178" t="inlineStr"/>
       <c r="AM178" t="n">
         <v>2.5</v>
       </c>
@@ -27269,14 +26929,10 @@
       </c>
       <c r="AK179" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL179" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL179" t="inlineStr"/>
       <c r="AM179" t="n">
         <v>0.4</v>
       </c>
@@ -27423,14 +27079,10 @@
       </c>
       <c r="AK180" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL180" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL180" t="inlineStr"/>
       <c r="AM180" t="n">
         <v>2.5</v>
       </c>
@@ -27577,14 +27229,10 @@
       </c>
       <c r="AK181" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL181" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL181" t="inlineStr"/>
       <c r="AM181" t="n">
         <v>2.5</v>
       </c>
@@ -27731,14 +27379,10 @@
       </c>
       <c r="AK182" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL182" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL182" t="inlineStr"/>
       <c r="AM182" t="n">
         <v>5</v>
       </c>
@@ -27883,14 +27527,10 @@
       </c>
       <c r="AK183" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL183" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL183" t="inlineStr"/>
       <c r="AM183" t="n">
         <v>5</v>
       </c>
@@ -28035,14 +27675,10 @@
       </c>
       <c r="AK184" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL184" t="inlineStr">
-        <is>
-          <t>Paraformaldehyde</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL184" t="inlineStr"/>
       <c r="AM184" t="n">
         <v>1</v>
       </c>
@@ -28179,14 +27815,10 @@
       </c>
       <c r="AK185" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL185" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL185" t="inlineStr"/>
       <c r="AM185" t="n">
         <v>3</v>
       </c>
@@ -28329,14 +27961,10 @@
       </c>
       <c r="AK186" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL186" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL186" t="inlineStr"/>
       <c r="AM186" t="n">
         <v>3</v>
       </c>
@@ -28479,20 +28107,14 @@
       </c>
       <c r="AK187" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL187" t="inlineStr">
-        <is>
-          <t>Methanol</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL187" t="inlineStr"/>
       <c r="AM187" t="n">
         <v>2.5</v>
       </c>
-      <c r="AN187" t="n">
-        <v>1</v>
-      </c>
+      <c r="AN187" t="inlineStr"/>
       <c r="AO187" t="inlineStr">
         <is>
           <t>97:3</t>
@@ -28511,13 +28133,13 @@
         <v>3</v>
       </c>
       <c r="AT187" t="n">
-        <v>0.3064103049153603</v>
+        <v>0.1018814263843573</v>
       </c>
       <c r="AU187" t="n">
-        <v>0.7660257622884007</v>
+        <v>0.2547035659608932</v>
       </c>
       <c r="AV187" t="n">
-        <v>3.508839222119954</v>
+        <v>1.166689041354884</v>
       </c>
     </row>
     <row r="188">
@@ -28633,14 +28255,10 @@
       </c>
       <c r="AK188" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL188" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL188" t="inlineStr"/>
       <c r="AM188" t="n">
         <v>3</v>
       </c>
@@ -28785,14 +28403,10 @@
       </c>
       <c r="AK189" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL189" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL189" t="inlineStr"/>
       <c r="AM189" t="n">
         <v>5</v>
       </c>
@@ -28937,14 +28551,10 @@
       </c>
       <c r="AK190" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL190" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL190" t="inlineStr"/>
       <c r="AM190" t="n">
         <v>2.5</v>
       </c>
@@ -29087,14 +28697,10 @@
       </c>
       <c r="AK191" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL191" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL191" t="inlineStr"/>
       <c r="AM191" t="n">
         <v>2.5</v>
       </c>
@@ -29237,14 +28843,10 @@
       </c>
       <c r="AK192" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL192" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL192" t="inlineStr"/>
       <c r="AM192" t="n">
         <v>1.825</v>
       </c>
@@ -29387,14 +28989,10 @@
       </c>
       <c r="AK193" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL193" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL193" t="inlineStr"/>
       <c r="AM193" t="n">
         <v>2.235294117647059</v>
       </c>
@@ -29537,14 +29135,10 @@
       </c>
       <c r="AK194" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL194" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL194" t="inlineStr"/>
       <c r="AM194" t="n">
         <v>2.235294117647059</v>
       </c>
@@ -29687,14 +29281,10 @@
       </c>
       <c r="AK195" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL195" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL195" t="inlineStr"/>
       <c r="AM195" t="n">
         <v>1.813333333333333</v>
       </c>
@@ -29837,14 +29427,10 @@
       </c>
       <c r="AK196" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL196" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL196" t="inlineStr"/>
       <c r="AM196" t="n">
         <v>2.235294117647059</v>
       </c>
@@ -29987,14 +29573,10 @@
       </c>
       <c r="AK197" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL197" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL197" t="inlineStr"/>
       <c r="AM197" t="n">
         <v>2.235294117647059</v>
       </c>
@@ -30137,14 +29719,10 @@
       </c>
       <c r="AK198" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL198" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL198" t="inlineStr"/>
       <c r="AM198" t="n">
         <v>2.235294117647059</v>
       </c>
@@ -30287,14 +29865,10 @@
       </c>
       <c r="AK199" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL199" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL199" t="inlineStr"/>
       <c r="AM199" t="n">
         <v>2.235294117647059</v>
       </c>
@@ -30437,14 +30011,10 @@
       </c>
       <c r="AK200" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL200" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL200" t="inlineStr"/>
       <c r="AM200" t="n">
         <v>2.102857142857143</v>
       </c>
@@ -30587,14 +30157,10 @@
       </c>
       <c r="AK201" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL201" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL201" t="inlineStr"/>
       <c r="AM201" t="n">
         <v>2.102857142857143</v>
       </c>
@@ -30737,14 +30303,10 @@
       </c>
       <c r="AK202" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL202" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL202" t="inlineStr"/>
       <c r="AM202" t="n">
         <v>2.102857142857143</v>
       </c>
@@ -30887,14 +30449,10 @@
       </c>
       <c r="AK203" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL203" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL203" t="inlineStr"/>
       <c r="AM203" t="n">
         <v>2.102857142857143</v>
       </c>
@@ -31037,14 +30595,10 @@
       </c>
       <c r="AK204" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL204" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL204" t="inlineStr"/>
       <c r="AM204" t="n">
         <v>2.102857142857143</v>
       </c>
@@ -31187,14 +30741,10 @@
       </c>
       <c r="AK205" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL205" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL205" t="inlineStr"/>
       <c r="AM205" t="n">
         <v>2.102857142857143</v>
       </c>
@@ -31337,14 +30887,10 @@
       </c>
       <c r="AK206" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL206" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL206" t="inlineStr"/>
       <c r="AM206" t="n">
         <v>2.102857142857143</v>
       </c>
@@ -31487,14 +31033,10 @@
       </c>
       <c r="AK207" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL207" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL207" t="inlineStr"/>
       <c r="AM207" t="n">
         <v>2.102857142857143</v>
       </c>
@@ -31637,14 +31179,10 @@
       </c>
       <c r="AK208" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL208" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL208" t="inlineStr"/>
       <c r="AM208" t="n">
         <v>2.102857142857143</v>
       </c>
@@ -31787,14 +31325,10 @@
       </c>
       <c r="AK209" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL209" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL209" t="inlineStr"/>
       <c r="AM209" t="n">
         <v>2.102857142857143</v>
       </c>
@@ -31940,11 +31474,7 @@
           <t>DMM</t>
         </is>
       </c>
-      <c r="AL210" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="AL210" t="inlineStr"/>
       <c r="AM210" t="n">
         <v>2</v>
       </c>
@@ -32086,11 +31616,7 @@
           <t>DMM</t>
         </is>
       </c>
-      <c r="AL211" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="AL211" t="inlineStr"/>
       <c r="AM211" t="n">
         <v>2</v>
       </c>
@@ -32232,11 +31758,7 @@
           <t>DMM</t>
         </is>
       </c>
-      <c r="AL212" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="AL212" t="inlineStr"/>
       <c r="AM212" t="n">
         <v>2</v>
       </c>
@@ -32378,11 +31900,7 @@
           <t>DMM</t>
         </is>
       </c>
-      <c r="AL213" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="AL213" t="inlineStr"/>
       <c r="AM213" t="n">
         <v>2</v>
       </c>
@@ -32523,12 +32041,12 @@
       </c>
       <c r="AK214" t="inlineStr">
         <is>
-          <t>Formalin</t>
+          <t>FORM</t>
         </is>
       </c>
       <c r="AL214" t="inlineStr">
         <is>
-          <t>Commercial formalin + methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM214" t="n">
@@ -32673,14 +32191,10 @@
       </c>
       <c r="AK215" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL215" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL215" t="inlineStr"/>
       <c r="AM215" t="n">
         <v>2.5</v>
       </c>
@@ -32825,14 +32339,10 @@
       </c>
       <c r="AK216" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL216" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL216" t="inlineStr"/>
       <c r="AM216" t="n">
         <v>2.5</v>
       </c>
@@ -32977,14 +32487,10 @@
       </c>
       <c r="AK217" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL217" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL217" t="inlineStr"/>
       <c r="AM217" t="n">
         <v>2.5</v>
       </c>
@@ -33129,14 +32635,10 @@
       </c>
       <c r="AK218" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL218" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL218" t="inlineStr"/>
       <c r="AM218" t="n">
         <v>2.5</v>
       </c>
@@ -33281,14 +32783,10 @@
       </c>
       <c r="AK219" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL219" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL219" t="inlineStr"/>
       <c r="AM219" t="n">
         <v>2.5</v>
       </c>
@@ -33433,14 +32931,10 @@
       </c>
       <c r="AK220" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL220" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL220" t="inlineStr"/>
       <c r="AM220" t="n">
         <v>2.5</v>
       </c>
@@ -33585,14 +33079,10 @@
       </c>
       <c r="AK221" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL221" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL221" t="inlineStr"/>
       <c r="AM221" t="n">
         <v>2.5</v>
       </c>
@@ -33737,14 +33227,10 @@
       </c>
       <c r="AK222" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL222" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL222" t="inlineStr"/>
       <c r="AM222" t="n">
         <v>2.5</v>
       </c>
@@ -33889,14 +33375,10 @@
       </c>
       <c r="AK223" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL223" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL223" t="inlineStr"/>
       <c r="AM223" t="n">
         <v>2.5</v>
       </c>
@@ -34041,14 +33523,10 @@
       </c>
       <c r="AK224" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL224" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL224" t="inlineStr"/>
       <c r="AM224" t="n">
         <v>2.5</v>
       </c>
@@ -34193,14 +33671,10 @@
       </c>
       <c r="AK225" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL225" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL225" t="inlineStr"/>
       <c r="AM225" t="n">
         <v>2.5</v>
       </c>
@@ -34345,14 +33819,10 @@
       </c>
       <c r="AK226" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL226" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL226" t="inlineStr"/>
       <c r="AM226" t="n">
         <v>2.5</v>
       </c>
@@ -34497,14 +33967,10 @@
       </c>
       <c r="AK227" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL227" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL227" t="inlineStr"/>
       <c r="AM227" t="n">
         <v>2.5</v>
       </c>
@@ -34649,14 +34115,10 @@
       </c>
       <c r="AK228" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL228" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL228" t="inlineStr"/>
       <c r="AM228" t="n">
         <v>2.5</v>
       </c>
@@ -34801,27 +34263,21 @@
       </c>
       <c r="AK229" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL229" t="inlineStr">
-        <is>
-          <t>Methanol</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL229" t="inlineStr"/>
       <c r="AM229" t="n">
         <v>2.5</v>
       </c>
-      <c r="AN229" t="n">
-        <v>1</v>
-      </c>
+      <c r="AN229" t="inlineStr"/>
       <c r="AO229" t="inlineStr">
         <is>
           <t>97:3</t>
         </is>
       </c>
       <c r="AP229" t="n">
-        <v>1.33</v>
+        <v>0.4433333333333334</v>
       </c>
       <c r="AQ229" t="n">
         <v>633</v>
@@ -34833,13 +34289,13 @@
         <v>3</v>
       </c>
       <c r="AT229" t="n">
-        <v>0.3064103049153603</v>
+        <v>0.1018814263843573</v>
       </c>
       <c r="AU229" t="n">
-        <v>0.7660257622884007</v>
+        <v>0.2547035659608932</v>
       </c>
       <c r="AV229" t="n">
-        <v>3.755916235591505</v>
+        <v>1.248842148334175</v>
       </c>
     </row>
     <row r="230">
@@ -34955,27 +34411,21 @@
       </c>
       <c r="AK230" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL230" t="inlineStr">
-        <is>
-          <t>Methanol</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL230" t="inlineStr"/>
       <c r="AM230" t="n">
         <v>2.5</v>
       </c>
-      <c r="AN230" t="n">
-        <v>1</v>
-      </c>
+      <c r="AN230" t="inlineStr"/>
       <c r="AO230" t="inlineStr">
         <is>
           <t>97:3</t>
         </is>
       </c>
       <c r="AP230" t="n">
-        <v>1.33</v>
+        <v>0.4433333333333334</v>
       </c>
       <c r="AQ230" t="n">
         <v>633</v>
@@ -34987,13 +34437,13 @@
         <v>3</v>
       </c>
       <c r="AT230" t="n">
-        <v>0.3064103049153603</v>
+        <v>0.1018814263843573</v>
       </c>
       <c r="AU230" t="n">
-        <v>0.7660257622884007</v>
+        <v>0.2547035659608932</v>
       </c>
       <c r="AV230" t="n">
-        <v>3.777668609547749</v>
+        <v>1.256074812674627</v>
       </c>
     </row>
     <row r="231">
@@ -35109,27 +34559,21 @@
       </c>
       <c r="AK231" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL231" t="inlineStr">
-        <is>
-          <t>Methanol</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL231" t="inlineStr"/>
       <c r="AM231" t="n">
         <v>2.5</v>
       </c>
-      <c r="AN231" t="n">
-        <v>1</v>
-      </c>
+      <c r="AN231" t="inlineStr"/>
       <c r="AO231" t="inlineStr">
         <is>
           <t>97:3</t>
         </is>
       </c>
       <c r="AP231" t="n">
-        <v>1.33</v>
+        <v>0.4433333333333334</v>
       </c>
       <c r="AQ231" t="n">
         <v>633</v>
@@ -35141,13 +34585,13 @@
         <v>3</v>
       </c>
       <c r="AT231" t="n">
-        <v>0.3064103049153603</v>
+        <v>0.1018814263843573</v>
       </c>
       <c r="AU231" t="n">
-        <v>0.7660257622884007</v>
+        <v>0.2547035659608932</v>
       </c>
       <c r="AV231" t="n">
-        <v>5.132311325271301</v>
+        <v>1.706493515652707</v>
       </c>
     </row>
     <row r="232">
@@ -35263,14 +34707,10 @@
       </c>
       <c r="AK232" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL232" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL232" t="inlineStr"/>
       <c r="AM232" t="n">
         <v>3.5</v>
       </c>
@@ -35405,14 +34845,10 @@
       </c>
       <c r="AK233" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL233" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL233" t="inlineStr"/>
       <c r="AM233" t="n">
         <v>3.5</v>
       </c>
@@ -35547,14 +34983,10 @@
       </c>
       <c r="AK234" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL234" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL234" t="inlineStr"/>
       <c r="AM234" t="n">
         <v>3.5</v>
       </c>
@@ -35689,14 +35121,10 @@
       </c>
       <c r="AK235" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL235" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL235" t="inlineStr"/>
       <c r="AM235" t="n">
         <v>3.5</v>
       </c>
@@ -35831,14 +35259,10 @@
       </c>
       <c r="AK236" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL236" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL236" t="inlineStr"/>
       <c r="AM236" t="n">
         <v>3.5</v>
       </c>
@@ -35973,14 +35397,10 @@
       </c>
       <c r="AK237" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL237" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL237" t="inlineStr"/>
       <c r="AM237" t="n">
         <v>3.5</v>
       </c>
@@ -36115,14 +35535,10 @@
       </c>
       <c r="AK238" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL238" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL238" t="inlineStr"/>
       <c r="AM238" t="n">
         <v>3.5</v>
       </c>
@@ -36257,14 +35673,10 @@
       </c>
       <c r="AK239" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL239" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL239" t="inlineStr"/>
       <c r="AM239" t="n">
         <v>3.5</v>
       </c>
@@ -36399,14 +35811,10 @@
       </c>
       <c r="AK240" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL240" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL240" t="inlineStr"/>
       <c r="AM240" t="n">
         <v>5</v>
       </c>
@@ -36551,14 +35959,10 @@
       </c>
       <c r="AK241" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL241" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL241" t="inlineStr"/>
       <c r="AM241" t="n">
         <v>5</v>
       </c>
@@ -36701,14 +36105,10 @@
       </c>
       <c r="AK242" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL242" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL242" t="inlineStr"/>
       <c r="AM242" t="n">
         <v>2.5</v>
       </c>
@@ -36853,14 +36253,10 @@
       </c>
       <c r="AK243" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL243" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL243" t="inlineStr"/>
       <c r="AM243" t="n">
         <v>5</v>
       </c>
@@ -37005,14 +36401,10 @@
       </c>
       <c r="AK244" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL244" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL244" t="inlineStr"/>
       <c r="AM244" t="n">
         <v>5</v>
       </c>
@@ -37157,14 +36549,10 @@
       </c>
       <c r="AK245" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL245" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL245" t="inlineStr"/>
       <c r="AM245" t="n">
         <v>5</v>
       </c>
@@ -37309,14 +36697,10 @@
       </c>
       <c r="AK246" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL246" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL246" t="inlineStr"/>
       <c r="AM246" t="n">
         <v>5</v>
       </c>
@@ -37461,14 +36845,10 @@
       </c>
       <c r="AK247" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL247" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL247" t="inlineStr"/>
       <c r="AM247" t="n">
         <v>5</v>
       </c>
@@ -37613,14 +36993,10 @@
       </c>
       <c r="AK248" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL248" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL248" t="inlineStr"/>
       <c r="AM248" t="n">
         <v>5</v>
       </c>
@@ -37765,14 +37141,10 @@
       </c>
       <c r="AK249" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL249" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL249" t="inlineStr"/>
       <c r="AM249" t="n">
         <v>5</v>
       </c>
@@ -37917,14 +37289,10 @@
       </c>
       <c r="AK250" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL250" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL250" t="inlineStr"/>
       <c r="AM250" t="n">
         <v>5</v>
       </c>
@@ -38069,14 +37437,10 @@
       </c>
       <c r="AK251" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL251" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL251" t="inlineStr"/>
       <c r="AM251" t="n">
         <v>5</v>
       </c>
@@ -38221,14 +37585,10 @@
       </c>
       <c r="AK252" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL252" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL252" t="inlineStr"/>
       <c r="AM252" t="n">
         <v>5</v>
       </c>
@@ -38373,14 +37733,10 @@
       </c>
       <c r="AK253" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL253" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL253" t="inlineStr"/>
       <c r="AM253" t="n">
         <v>5</v>
       </c>
@@ -38525,14 +37881,10 @@
       </c>
       <c r="AK254" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL254" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL254" t="inlineStr"/>
       <c r="AM254" t="n">
         <v>5</v>
       </c>
@@ -38677,14 +38029,10 @@
       </c>
       <c r="AK255" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL255" t="inlineStr">
-        <is>
-          <t>Paraformaldehyde</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL255" t="inlineStr"/>
       <c r="AM255" t="n">
         <v>1</v>
       </c>
@@ -38821,14 +38169,10 @@
       </c>
       <c r="AK256" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL256" t="inlineStr">
-        <is>
-          <t>Paraformaldehyde</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL256" t="inlineStr"/>
       <c r="AM256" t="n">
         <v>1</v>
       </c>
@@ -38965,14 +38309,10 @@
       </c>
       <c r="AK257" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL257" t="inlineStr">
-        <is>
-          <t>Paraformaldehyde</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL257" t="inlineStr"/>
       <c r="AM257" t="n">
         <v>1</v>
       </c>
@@ -39109,14 +38449,10 @@
       </c>
       <c r="AK258" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL258" t="inlineStr">
-        <is>
-          <t>Paraformaldehyde</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL258" t="inlineStr"/>
       <c r="AM258" t="n">
         <v>1</v>
       </c>
@@ -39251,14 +38587,10 @@
       </c>
       <c r="AK259" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL259" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL259" t="inlineStr"/>
       <c r="AM259" t="n">
         <v>5</v>
       </c>
@@ -39403,14 +38735,10 @@
       </c>
       <c r="AK260" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL260" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL260" t="inlineStr"/>
       <c r="AM260" t="n">
         <v>3</v>
       </c>
@@ -39555,14 +38883,10 @@
       </c>
       <c r="AK261" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL261" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL261" t="inlineStr"/>
       <c r="AM261" t="n">
         <v>3</v>
       </c>
@@ -39705,14 +39029,10 @@
       </c>
       <c r="AK262" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL262" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL262" t="inlineStr"/>
       <c r="AM262" t="n">
         <v>3</v>
       </c>
@@ -39858,11 +39178,7 @@
           <t>DMM</t>
         </is>
       </c>
-      <c r="AL263" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="AL263" t="inlineStr"/>
       <c r="AM263" t="n">
         <v>2.5</v>
       </c>
@@ -40009,14 +39325,10 @@
       </c>
       <c r="AK264" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL264" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL264" t="inlineStr"/>
       <c r="AM264" t="n">
         <v>3</v>
       </c>
@@ -40161,14 +39473,10 @@
       </c>
       <c r="AK265" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL265" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL265" t="inlineStr"/>
       <c r="AM265" t="n">
         <v>3</v>
       </c>
@@ -40313,14 +39621,10 @@
       </c>
       <c r="AK266" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL266" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL266" t="inlineStr"/>
       <c r="AM266" t="n">
         <v>3</v>
       </c>
@@ -40465,14 +39769,10 @@
       </c>
       <c r="AK267" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL267" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL267" t="inlineStr"/>
       <c r="AM267" t="n">
         <v>2.5</v>
       </c>
@@ -40615,14 +39915,10 @@
       </c>
       <c r="AK268" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL268" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL268" t="inlineStr"/>
       <c r="AM268" t="n">
         <v>10</v>
       </c>
@@ -40767,14 +40063,10 @@
       </c>
       <c r="AK269" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL269" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL269" t="inlineStr"/>
       <c r="AM269" t="n">
         <v>10</v>
       </c>
@@ -40919,14 +40211,10 @@
       </c>
       <c r="AK270" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL270" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL270" t="inlineStr"/>
       <c r="AM270" t="n">
         <v>10</v>
       </c>
@@ -41071,14 +40359,10 @@
       </c>
       <c r="AK271" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL271" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL271" t="inlineStr"/>
       <c r="AM271" t="n">
         <v>7.5</v>
       </c>
@@ -41223,14 +40507,10 @@
       </c>
       <c r="AK272" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL272" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL272" t="inlineStr"/>
       <c r="AM272" t="n">
         <v>5</v>
       </c>
@@ -41375,14 +40655,10 @@
       </c>
       <c r="AK273" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL273" t="inlineStr">
-        <is>
-          <t>Paraformaldehyde</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL273" t="inlineStr"/>
       <c r="AM273" t="n">
         <v>1</v>
       </c>
@@ -41519,14 +40795,10 @@
       </c>
       <c r="AK274" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL274" t="inlineStr">
-        <is>
-          <t>Paraformaldehyde</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL274" t="inlineStr"/>
       <c r="AM274" t="n">
         <v>1</v>
       </c>
@@ -41663,14 +40935,10 @@
       </c>
       <c r="AK275" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL275" t="inlineStr">
-        <is>
-          <t>Paraformaldehyde</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL275" t="inlineStr"/>
       <c r="AM275" t="n">
         <v>1</v>
       </c>
@@ -41807,14 +41075,10 @@
       </c>
       <c r="AK276" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL276" t="inlineStr">
-        <is>
-          <t>Paraformaldehyde</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL276" t="inlineStr"/>
       <c r="AM276" t="n">
         <v>1</v>
       </c>
@@ -41951,14 +41215,10 @@
       </c>
       <c r="AK277" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL277" t="inlineStr">
-        <is>
-          <t>Paraformaldehyde</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL277" t="inlineStr"/>
       <c r="AM277" t="n">
         <v>1</v>
       </c>
@@ -42095,14 +41355,10 @@
       </c>
       <c r="AK278" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL278" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL278" t="inlineStr"/>
       <c r="AM278" t="n">
         <v>3</v>
       </c>
@@ -42245,14 +41501,10 @@
       </c>
       <c r="AK279" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL279" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL279" t="inlineStr"/>
       <c r="AM279" t="n">
         <v>3</v>
       </c>
@@ -42395,14 +41647,10 @@
       </c>
       <c r="AK280" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL280" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL280" t="inlineStr"/>
       <c r="AM280" t="n">
         <v>3</v>
       </c>
@@ -42547,14 +41795,10 @@
       </c>
       <c r="AK281" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL281" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL281" t="inlineStr"/>
       <c r="AM281" t="n">
         <v>3</v>
       </c>
@@ -42699,14 +41943,10 @@
       </c>
       <c r="AK282" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL282" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL282" t="inlineStr"/>
       <c r="AM282" t="n">
         <v>3</v>
       </c>
@@ -42851,14 +42091,10 @@
       </c>
       <c r="AK283" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL283" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL283" t="inlineStr"/>
       <c r="AM283" t="n">
         <v>3</v>
       </c>
@@ -43006,11 +42242,7 @@
           <t>DMM</t>
         </is>
       </c>
-      <c r="AL284" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="AL284" t="inlineStr"/>
       <c r="AM284" t="n">
         <v>1.6</v>
       </c>
@@ -43148,11 +42380,7 @@
           <t>DMM</t>
         </is>
       </c>
-      <c r="AL285" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="AL285" t="inlineStr"/>
       <c r="AM285" t="n">
         <v>1.6</v>
       </c>
@@ -43287,14 +42515,10 @@
       </c>
       <c r="AK286" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL286" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL286" t="inlineStr"/>
       <c r="AM286" t="n">
         <v>3</v>
       </c>
@@ -43439,14 +42663,10 @@
       </c>
       <c r="AK287" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL287" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL287" t="inlineStr"/>
       <c r="AM287" t="n">
         <v>3</v>
       </c>
@@ -43591,14 +42811,10 @@
       </c>
       <c r="AK288" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL288" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL288" t="inlineStr"/>
       <c r="AM288" t="n">
         <v>3</v>
       </c>
@@ -43743,14 +42959,10 @@
       </c>
       <c r="AK289" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL289" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL289" t="inlineStr"/>
       <c r="AM289" t="n">
         <v>3</v>
       </c>
@@ -43895,14 +43107,10 @@
       </c>
       <c r="AK290" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL290" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL290" t="inlineStr"/>
       <c r="AM290" t="n">
         <v>3</v>
       </c>
@@ -44047,14 +43255,10 @@
       </c>
       <c r="AK291" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL291" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL291" t="inlineStr"/>
       <c r="AM291" t="n">
         <v>2.5</v>
       </c>
@@ -44199,14 +43403,10 @@
       </c>
       <c r="AK292" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL292" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL292" t="inlineStr"/>
       <c r="AM292" t="n">
         <v>2.5</v>
       </c>
@@ -44351,14 +43551,10 @@
       </c>
       <c r="AK293" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL293" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL293" t="inlineStr"/>
       <c r="AM293" t="n">
         <v>2.5</v>
       </c>
@@ -44503,14 +43699,10 @@
       </c>
       <c r="AK294" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL294" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL294" t="inlineStr"/>
       <c r="AM294" t="n">
         <v>2.5</v>
       </c>
@@ -44655,14 +43847,10 @@
       </c>
       <c r="AK295" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL295" t="inlineStr">
-        <is>
-          <t>Paraformaldehyde</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL295" t="inlineStr"/>
       <c r="AM295" t="n">
         <v>1</v>
       </c>
@@ -44799,14 +43987,10 @@
       </c>
       <c r="AK296" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL296" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL296" t="inlineStr"/>
       <c r="AM296" t="n">
         <v>2.5</v>
       </c>
@@ -44951,14 +44135,10 @@
       </c>
       <c r="AK297" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL297" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL297" t="inlineStr"/>
       <c r="AM297" t="n">
         <v>2.5</v>
       </c>
@@ -45103,14 +44283,10 @@
       </c>
       <c r="AK298" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL298" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL298" t="inlineStr"/>
       <c r="AM298" t="n">
         <v>2.5</v>
       </c>
@@ -45255,14 +44431,10 @@
       </c>
       <c r="AK299" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL299" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL299" t="inlineStr"/>
       <c r="AM299" t="n">
         <v>2.5</v>
       </c>
@@ -45407,14 +44579,10 @@
       </c>
       <c r="AK300" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL300" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL300" t="inlineStr"/>
       <c r="AM300" t="n">
         <v>5</v>
       </c>
@@ -45559,14 +44727,10 @@
       </c>
       <c r="AK301" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL301" t="inlineStr">
-        <is>
-          <t>Paraformaldehyde</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL301" t="inlineStr"/>
       <c r="AM301" t="n">
         <v>1</v>
       </c>
@@ -45703,14 +44867,10 @@
       </c>
       <c r="AK302" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL302" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL302" t="inlineStr"/>
       <c r="AM302" t="n">
         <v>3</v>
       </c>
@@ -45857,14 +45017,10 @@
       </c>
       <c r="AK303" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL303" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL303" t="inlineStr"/>
       <c r="AM303" t="n">
         <v>5</v>
       </c>
@@ -46009,14 +45165,10 @@
       </c>
       <c r="AK304" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL304" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL304" t="inlineStr"/>
       <c r="AM304" t="n">
         <v>3</v>
       </c>
@@ -46161,14 +45313,10 @@
       </c>
       <c r="AK305" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL305" t="inlineStr">
-        <is>
-          <t>Paraformaldehyde</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL305" t="inlineStr"/>
       <c r="AM305" t="n">
         <v>1</v>
       </c>
@@ -46305,14 +45453,10 @@
       </c>
       <c r="AK306" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL306" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL306" t="inlineStr"/>
       <c r="AM306" t="n">
         <v>3</v>
       </c>
@@ -46457,14 +45601,10 @@
       </c>
       <c r="AK307" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL307" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL307" t="inlineStr"/>
       <c r="AM307" t="n">
         <v>5</v>
       </c>
@@ -46609,14 +45749,10 @@
       </c>
       <c r="AK308" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL308" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL308" t="inlineStr"/>
       <c r="AM308" t="n">
         <v>5</v>
       </c>
@@ -46761,14 +45897,10 @@
       </c>
       <c r="AK309" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL309" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL309" t="inlineStr"/>
       <c r="AM309" t="n">
         <v>5</v>
       </c>
@@ -46913,14 +46045,10 @@
       </c>
       <c r="AK310" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL310" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL310" t="inlineStr"/>
       <c r="AM310" t="n">
         <v>5</v>
       </c>
@@ -47065,14 +46193,10 @@
       </c>
       <c r="AK311" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL311" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL311" t="inlineStr"/>
       <c r="AM311" t="n">
         <v>5</v>
       </c>
@@ -47085,11 +46209,7 @@
       <c r="AP311" t="n">
         <v>1.2</v>
       </c>
-      <c r="AQ311" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
+      <c r="AQ311" t="inlineStr"/>
       <c r="AR311" t="n">
         <v>1</v>
       </c>
@@ -47219,14 +46339,10 @@
       </c>
       <c r="AK312" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL312" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL312" t="inlineStr"/>
       <c r="AM312" t="n">
         <v>5</v>
       </c>
@@ -47239,11 +46355,7 @@
       <c r="AP312" t="n">
         <v>1.2</v>
       </c>
-      <c r="AQ312" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
+      <c r="AQ312" t="inlineStr"/>
       <c r="AR312" t="n">
         <v>1</v>
       </c>
@@ -47373,14 +46485,10 @@
       </c>
       <c r="AK313" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL313" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL313" t="inlineStr"/>
       <c r="AM313" t="n">
         <v>5</v>
       </c>
@@ -47393,11 +46501,7 @@
       <c r="AP313" t="n">
         <v>1.2</v>
       </c>
-      <c r="AQ313" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
+      <c r="AQ313" t="inlineStr"/>
       <c r="AR313" t="n">
         <v>1</v>
       </c>
@@ -47527,14 +46631,10 @@
       </c>
       <c r="AK314" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL314" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL314" t="inlineStr"/>
       <c r="AM314" t="n">
         <v>5</v>
       </c>
@@ -47679,14 +46779,10 @@
       </c>
       <c r="AK315" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL315" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL315" t="inlineStr"/>
       <c r="AM315" t="n">
         <v>5</v>
       </c>

--- a/data/data_clean.xlsx
+++ b/data/data_clean.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV315"/>
+  <dimension ref="A1:AW315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,6 +669,11 @@
           <t>STY MA+AA (mmol/h/g)</t>
         </is>
       </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>doi</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -817,6 +822,11 @@
       <c r="AV2" t="n">
         <v>0.5955842332613392</v>
       </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6b03079</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -959,6 +969,11 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="inlineStr"/>
       <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>10.1039/C6CY00620E</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1101,6 +1116,11 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>10.1039/C6CY00620E</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1243,6 +1263,11 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>10.1039/C6CY00620E</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1397,6 +1422,11 @@
       <c r="AV6" t="n">
         <v>0.6996076572598475</v>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.2c03415</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1545,6 +1575,11 @@
       <c r="AV7" t="n">
         <v>0.771274570811601</v>
       </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>10.1039/D2RA06960A</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1693,6 +1728,11 @@
       <c r="AV8" t="n">
         <v>0.6732217411871608</v>
       </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>10.1039/D2RA06960A</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1847,6 +1887,11 @@
       <c r="AV9" t="n">
         <v>13.29038020513888</v>
       </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-017-2014-8</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -2001,6 +2046,11 @@
       <c r="AV10" t="n">
         <v>3.236708989464488</v>
       </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-017-2014-8</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2155,6 +2205,11 @@
       <c r="AV11" t="n">
         <v>6.477051706276816</v>
       </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-017-2014-8</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2309,6 +2364,11 @@
       <c r="AV12" t="n">
         <v>6.838899172791308</v>
       </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-017-2014-8</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2463,6 +2523,11 @@
       <c r="AV13" t="n">
         <v>11.07093542974365</v>
       </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-017-2014-8</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2617,6 +2682,11 @@
       <c r="AV14" t="n">
         <v>12.03544330602205</v>
       </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-017-2014-8</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2771,6 +2841,11 @@
       <c r="AV15" t="n">
         <v>12.52299082227291</v>
       </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-017-2014-8</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2925,6 +3000,11 @@
       <c r="AV16" t="n">
         <v>13.17401120834511</v>
       </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-017-2014-8</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -3079,6 +3159,11 @@
       <c r="AV17" t="n">
         <v>14.5255783384156</v>
       </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-017-2014-8</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3233,6 +3318,11 @@
       <c r="AV18" t="n">
         <v>16.17609804930094</v>
       </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-017-2014-8</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3385,6 +3475,11 @@
       <c r="AV19" t="n">
         <v>17.82231112036662</v>
       </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-017-2014-8</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3537,6 +3632,11 @@
       <c r="AV20" t="n">
         <v>13.33927851142462</v>
       </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>10.1039/C7RA10008F</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3689,6 +3789,11 @@
       <c r="AV21" t="n">
         <v>16.22015138578957</v>
       </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>10.1039/C7RA10008F</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3841,6 +3946,11 @@
       <c r="AV22" t="n">
         <v>11.86156272330321</v>
       </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>10.1039/C7RA10008F</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3993,6 +4103,11 @@
       <c r="AV23" t="n">
         <v>14.56074923027617</v>
       </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>10.1039/C7RA10008F</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -4145,6 +4260,11 @@
       <c r="AV24" t="n">
         <v>15.50390335078208</v>
       </c>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>10.1039/C7RA10008F</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -4297,6 +4417,11 @@
       <c r="AV25" t="n">
         <v>16.61322199099661</v>
       </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>10.1039/C7RA10008F</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -4449,6 +4574,11 @@
       <c r="AV26" t="n">
         <v>16.94034717396508</v>
       </c>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>10.1039/C7RA10008F</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4603,6 +4733,11 @@
       <c r="AV27" t="n">
         <v>12.9917380612777</v>
       </c>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-018-2535-9</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4757,6 +4892,11 @@
       <c r="AV28" t="n">
         <v>11.9741669991213</v>
       </c>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-018-2535-9</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4911,6 +5051,11 @@
       <c r="AV29" t="n">
         <v>16.57934578273182</v>
       </c>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-018-2535-9</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -5065,6 +5210,11 @@
       <c r="AV30" t="n">
         <v>17.10723081280191</v>
       </c>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-018-2535-9</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -5205,6 +5355,11 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AU31" t="inlineStr"/>
       <c r="AV31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.7b02522</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -5353,6 +5508,11 @@
       <c r="AV32" t="n">
         <v>1.037342752224622</v>
       </c>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>10.1002/cjce.22889</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -5501,6 +5661,11 @@
       <c r="AV33" t="n">
         <v>0.6083303095464363</v>
       </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>10.1002/cjce.22889</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -5649,6 +5814,11 @@
       <c r="AV34" t="n">
         <v>1.035357229892009</v>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>10.1002/cjce.22889</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5801,6 +5971,11 @@
       <c r="AV35" t="n">
         <v>2.264403873433229</v>
       </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>10.1016/j.cjche.2021.11.025</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5953,6 +6128,11 @@
       <c r="AV36" t="n">
         <v>2.403258827936211</v>
       </c>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>10.1016/j.cjche.2021.11.025</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -6105,6 +6285,11 @@
       <c r="AV37" t="n">
         <v>1.506042198840025</v>
       </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>10.1016/j.cjche.2021.11.025</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -6257,6 +6442,11 @@
       <c r="AV38" t="n">
         <v>1.185607688448531</v>
       </c>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>10.1016/j.cjche.2021.11.025</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -6397,6 +6587,11 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AU39" t="inlineStr"/>
       <c r="AV39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>10.1016/S1872‐2067(18)63069‐4</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -6551,6 +6746,11 @@
       <c r="AV40" t="n">
         <v>0.3794963157532329</v>
       </c>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.1c04460</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -6702,6 +6902,11 @@
       </c>
       <c r="AV41" t="n">
         <v>0</v>
+      </c>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>10.1016/j.cjche.2021.11.025</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -6841,6 +7046,11 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AU42" t="inlineStr"/>
       <c r="AV42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>10.1021/i360017a011</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -6989,6 +7199,11 @@
       <c r="AV43" t="n">
         <v>3.702138292163938</v>
       </c>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>10.1002/jctb.7032</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -7137,6 +7352,11 @@
       <c r="AV44" t="n">
         <v>5.624765755944122</v>
       </c>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>10.1002/jctb.7032</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -7285,6 +7505,11 @@
       <c r="AV45" t="n">
         <v>5.479437961698586</v>
       </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>10.1002/jctb.7032</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -7433,6 +7658,11 @@
       <c r="AV46" t="n">
         <v>4.441654779239522</v>
       </c>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>10.1002/jctb.7032</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -7581,6 +7811,11 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AU47" t="inlineStr"/>
       <c r="AV47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>10.1021/acs.energyfuels.1c03082</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -7719,6 +7954,11 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AU48" t="inlineStr"/>
       <c r="AV48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>10.1021/i360017a011</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -7873,6 +8113,11 @@
       <c r="AV49" t="n">
         <v>0.2861124139451171</v>
       </c>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>10.1016/j.cej.2023.145655</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -8021,6 +8266,11 @@
       <c r="AV50" t="n">
         <v>0.2759276079913607</v>
       </c>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>10.1002/cjce.22889</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -8169,6 +8419,11 @@
       <c r="AV51" t="n">
         <v>0.08603980431965444</v>
       </c>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>10.1002/cjce.22889</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -8317,6 +8572,11 @@
       <c r="AV52" t="n">
         <v>0.2703290256155508</v>
       </c>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>10.1002/cjce.22889</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -8465,6 +8725,11 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AU53" t="inlineStr"/>
       <c r="AV53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>10.1016/j.jiec.2016.11.002</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -8613,6 +8878,11 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AU54" t="inlineStr"/>
       <c r="AV54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>10.1016/j.jiec.2016.11.002</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -8761,6 +9031,11 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AU55" t="inlineStr"/>
       <c r="AV55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>10.1016/j.jiec.2016.11.002</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -8915,6 +9190,11 @@
       <c r="AV56" t="n">
         <v>1.463177140327438</v>
       </c>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.2c03415</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -9069,6 +9349,11 @@
       <c r="AV57" t="n">
         <v>3.419587658065798</v>
       </c>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.2c03415</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -9223,6 +9508,11 @@
       <c r="AV58" t="n">
         <v>6.069304012704706</v>
       </c>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.2c03415</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -9375,6 +9665,11 @@
       <c r="AV59" t="n">
         <v>0.3024225830464325</v>
       </c>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>10.4028/www.scientific.net/AMR.629.376</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -9527,6 +9822,11 @@
       <c r="AV60" t="n">
         <v>1.445984926025873</v>
       </c>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>10.4028/www.scientific.net/AMR.629.376</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -9679,6 +9979,11 @@
       <c r="AV61" t="n">
         <v>1.77628058993208</v>
       </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>10.4028/www.scientific.net/AMR.629.376</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -9831,6 +10136,11 @@
       <c r="AV62" t="n">
         <v>0.2558602546059374</v>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>10.1556/JFC-D-14-00035</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -9985,6 +10295,11 @@
       <c r="AV63" t="n">
         <v>3.634130663173834</v>
       </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>10.1016/j.cattod.2020.06.026</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -10139,6 +10454,11 @@
       <c r="AV64" t="n">
         <v>2.371075264188601</v>
       </c>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>10.1016/j.cattod.2020.06.026</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -10293,6 +10613,11 @@
       <c r="AV65" t="n">
         <v>3.786562125771817</v>
       </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>10.1016/j.cattod.2020.06.026</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -10447,6 +10772,11 @@
       <c r="AV66" t="n">
         <v>1.891540793050767</v>
       </c>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>10.1016/j.cattod.2020.06.026</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -10601,6 +10931,11 @@
       <c r="AV67" t="n">
         <v>5.376879068075143</v>
       </c>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>10.1016/j.cej.2023.145655</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -10755,6 +11090,11 @@
       <c r="AV68" t="n">
         <v>7.903561347560993</v>
       </c>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>10.1016/j.cej.2023.145655</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -10909,6 +11249,11 @@
       <c r="AV69" t="n">
         <v>13.45604648323464</v>
       </c>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>10.1007/s11144-018-1419-8</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -11057,6 +11402,11 @@
       <c r="AV70" t="n">
         <v>0.05598754483801297</v>
       </c>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>10.1002/cjce.22889</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -11204,6 +11554,11 @@
       </c>
       <c r="AV71" t="n">
         <v>0.150405173650108</v>
+      </c>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>10.1002/cjce.22889</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -11349,6 +11704,11 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AU72" t="inlineStr"/>
       <c r="AV72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-018-2609-8</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -11493,6 +11853,11 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AU73" t="inlineStr"/>
       <c r="AV73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-018-2609-8</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -11637,6 +12002,11 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AU74" t="inlineStr"/>
       <c r="AV74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-018-2609-8</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -11785,6 +12155,11 @@
       <c r="AV75" t="n">
         <v>21.21964717062635</v>
       </c>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>10.1016/j.jiec.2014.11.014</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -11933,6 +12308,11 @@
       <c r="AV76" t="n">
         <v>13.61464794816415</v>
       </c>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>10.1016/j.jiec.2014.11.014</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -12087,6 +12467,11 @@
       <c r="AV77" t="n">
         <v>10.39883272224373</v>
       </c>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>10.1007/s11144-018-1419-8</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -12235,6 +12620,11 @@
       <c r="AV78" t="n">
         <v>0.04646637978401728</v>
       </c>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>10.1002/cjce.22889</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -12382,6 +12772,11 @@
       </c>
       <c r="AV79" t="n">
         <v>0.2214445889416847</v>
+      </c>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>10.1002/cjce.22889</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -12527,6 +12922,11 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AU80" t="inlineStr"/>
       <c r="AV80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.7b02841</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -12671,6 +13071,11 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AU81" t="inlineStr"/>
       <c r="AV81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.7b02841</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -12825,6 +13230,11 @@
       <c r="AV82" t="n">
         <v>1.495361048493642</v>
       </c>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.1c04460</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -12979,6 +13389,11 @@
       <c r="AV83" t="n">
         <v>1.64176449330127</v>
       </c>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.1c04460</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -13133,6 +13548,11 @@
       <c r="AV84" t="n">
         <v>1.091613565400359</v>
       </c>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.2c00444</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -13287,6 +13707,11 @@
       <c r="AV85" t="n">
         <v>2.13088949410344</v>
       </c>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.2c00444</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -13441,6 +13866,11 @@
       <c r="AV86" t="n">
         <v>3.753356231719042</v>
       </c>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.2c00444</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -13595,6 +14025,11 @@
       <c r="AV87" t="n">
         <v>2.139319741550428</v>
       </c>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>10.1080/00219592.2023.2300818</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -13749,6 +14184,11 @@
       <c r="AV88" t="n">
         <v>3.357085553868227</v>
       </c>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.4c00771</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -13903,6 +14343,11 @@
       <c r="AV89" t="n">
         <v>1.735801660800266</v>
       </c>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>10.1016/j.ces.2024.120716</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -14057,6 +14502,11 @@
       <c r="AV90" t="n">
         <v>3.093893946960023</v>
       </c>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>10.1016/j.ces.2024.120716</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -14209,6 +14659,11 @@
       <c r="AV91" t="n">
         <v>1.568635433144139</v>
       </c>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>10.4028/www.scientific.net/AMR.629.376</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -14361,6 +14816,11 @@
       <c r="AV92" t="n">
         <v>0.6821794308876921</v>
       </c>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>10.1556/JFC-D-14-00035</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -14513,6 +14973,11 @@
       <c r="AV93" t="n">
         <v>0.950415014073698</v>
       </c>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>10.1556/JFC-D-14-00035</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -14665,6 +15130,11 @@
       <c r="AV94" t="n">
         <v>0.8147204197217046</v>
       </c>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>10.1556/JFC-D-14-00035</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -14817,6 +15287,11 @@
       <c r="AV95" t="n">
         <v>0.7069439946984121</v>
       </c>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>10.1556/JFC-D-14-00035</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -14969,6 +15444,11 @@
       <c r="AV96" t="n">
         <v>0.5910992060277078</v>
       </c>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>10.1039/C5RA05133A</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -15121,6 +15601,11 @@
       <c r="AV97" t="n">
         <v>0.8025740804504577</v>
       </c>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>10.1039/C5RA05133A</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -15273,6 +15758,11 @@
       <c r="AV98" t="n">
         <v>0.9489437332901238</v>
       </c>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>10.1039/C5RA05133A</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -15425,6 +15915,11 @@
       <c r="AV99" t="n">
         <v>1.06557107267277</v>
       </c>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>10.1039/C5RA05133A</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -15577,6 +16072,11 @@
       <c r="AV100" t="n">
         <v>1.07774902778903</v>
       </c>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>10.1039/C5RA05133A</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -15728,6 +16228,11 @@
       </c>
       <c r="AV101" t="n">
         <v>0.3129223271610692</v>
+      </c>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>10.1556/JFC-D-14-00035</t>
+        </is>
       </c>
     </row>
     <row r="102">
@@ -15867,6 +16372,11 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AU102" t="inlineStr"/>
       <c r="AV102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>10.1021/i360017a011</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -16005,6 +16515,11 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AU103" t="inlineStr"/>
       <c r="AV103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>10.1021/i360017a011</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -16143,6 +16658,11 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AU104" t="inlineStr"/>
       <c r="AV104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>10.1021/i360017a011</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -16281,6 +16801,11 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AU105" t="inlineStr"/>
       <c r="AV105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>10.1021/i360017a011</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -16419,6 +16944,11 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AU106" t="inlineStr"/>
       <c r="AV106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>10.1021/i360017a011</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -16557,6 +17087,11 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AU107" t="inlineStr"/>
       <c r="AV107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>10.1021/i360017a011</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -16695,6 +17230,11 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AU108" t="inlineStr"/>
       <c r="AV108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>10.1021/i360017a011</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -16833,6 +17373,11 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AU109" t="inlineStr"/>
       <c r="AV109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>10.1021/i360017a011</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -16971,6 +17516,11 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AU110" t="inlineStr"/>
       <c r="AV110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>10.1021/i360017a011</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -17109,6 +17659,11 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AU111" t="inlineStr"/>
       <c r="AV111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>10.1021/i360017a011</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -17247,6 +17802,11 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AU112" t="inlineStr"/>
       <c r="AV112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>10.1021/i360017a011</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -17397,6 +17957,11 @@
       <c r="AV113" t="n">
         <v>0.7978073570911253</v>
       </c>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>10.1039/D2CY00447J</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -17539,6 +18104,11 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AU114" t="inlineStr"/>
       <c r="AV114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>10.1039/c7cc04574c</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -17689,6 +18259,11 @@
       <c r="AV115" t="n">
         <v>0.1913143370876304</v>
       </c>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>10.1039/D2CY00447J</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -17831,6 +18406,11 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AU116" t="inlineStr"/>
       <c r="AV116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>10.1039/c7cc04574c</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -17973,6 +18553,11 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AU117" t="inlineStr"/>
       <c r="AV117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>10.1039/c7cc04574c</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -18123,6 +18708,11 @@
       <c r="AV118" t="n">
         <v>0.5785930125115488</v>
       </c>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>10.1039/D2CY00447J</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -18265,6 +18855,11 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AU119" t="inlineStr"/>
       <c r="AV119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>10.1039/c7cc04574c</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -18407,6 +19002,11 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AU120" t="inlineStr"/>
       <c r="AV120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>10.1039/c7cc04574c</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -18549,6 +19149,11 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AU121" t="inlineStr"/>
       <c r="AV121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>10.1039/c7cc04574c</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -18689,6 +19294,11 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AU122" t="inlineStr"/>
       <c r="AV122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>10.1016/S1872‐2067(18)63069‐4</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -18829,6 +19439,11 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AU123" t="inlineStr"/>
       <c r="AV123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>10.1016/S1872‐2067(18)63069‐4</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -18969,6 +19584,11 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AU124" t="inlineStr"/>
       <c r="AV124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>10.1016/S1872-2067(18)63145-6</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -19109,6 +19729,11 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AU125" t="inlineStr"/>
       <c r="AV125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>10.1016/S1872-2067(18)63145-6</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -19249,6 +19874,11 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AU126" t="inlineStr"/>
       <c r="AV126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>10.1016/S1872-2067(18)63145-6</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -19397,6 +20027,11 @@
       <c r="AV127" t="n">
         <v>1.06119671353295</v>
       </c>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>10.1039/D2CY00447J</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -19545,6 +20180,11 @@
       <c r="AV128" t="n">
         <v>0.656978747846064</v>
       </c>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>10.1039/D2CY00447J</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -19693,6 +20333,11 @@
       <c r="AV129" t="n">
         <v>1.498628973853105</v>
       </c>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>10.1039/D2CY00447J</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -19841,6 +20486,11 @@
       <c r="AV130" t="n">
         <v>0.9854681217690963</v>
       </c>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>10.1039/D2CY00447J</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -19983,6 +20633,11 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AU131" t="inlineStr"/>
       <c r="AV131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>10.1039/c7cc04574c</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -20127,6 +20782,11 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AU132" t="inlineStr"/>
       <c r="AV132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.7b02841</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -20271,6 +20931,11 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AU133" t="inlineStr"/>
       <c r="AV133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.7b02841</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -20409,6 +21074,11 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AU134" t="inlineStr"/>
       <c r="AV134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>10.1021/i360017a011</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -20557,6 +21227,11 @@
       <c r="AV135" t="n">
         <v>1.586163584424854</v>
       </c>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>10.1039/D2RA06960A</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -20704,6 +21379,11 @@
       </c>
       <c r="AV136" t="n">
         <v>4.07557385098487</v>
+      </c>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>10.1002/jctb.6360</t>
+        </is>
       </c>
     </row>
     <row r="137">
@@ -20849,6 +21529,11 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AU137" t="inlineStr"/>
       <c r="AV137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.7b02841</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -20997,6 +21682,11 @@
       <c r="AV138" t="n">
         <v>0.5065107991360693</v>
       </c>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6b03079</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -21145,6 +21835,11 @@
       <c r="AV139" t="n">
         <v>1.113617612184385</v>
       </c>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>10.1039/D2RA06960A</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -21293,6 +21988,11 @@
       <c r="AV140" t="n">
         <v>0.1455692410367171</v>
       </c>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>10.1002/cjce.22889</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -21440,6 +22140,11 @@
       </c>
       <c r="AV141" t="n">
         <v>0.2176466184881211</v>
+      </c>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>10.1002/cjce.22889</t>
+        </is>
       </c>
     </row>
     <row r="142">
@@ -21585,6 +22290,11 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AU142" t="inlineStr"/>
       <c r="AV142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.7b02841</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -21733,6 +22443,11 @@
       <c r="AV143" t="n">
         <v>0.05560799136069117</v>
       </c>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6b03079</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -21881,6 +22596,11 @@
       <c r="AV144" t="n">
         <v>3.739272570194384</v>
       </c>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>10.1016/j.jiec.2014.11.014</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -22035,6 +22755,11 @@
       <c r="AV145" t="n">
         <v>0</v>
       </c>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>10.1007/s11144-018-1419-8</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -22188,6 +22913,11 @@
       </c>
       <c r="AV146" t="n">
         <v>3.197042635550025</v>
+      </c>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>10.1007/s11144-018-1419-8</t>
+        </is>
       </c>
     </row>
     <row r="147">
@@ -22327,6 +23057,11 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AU147" t="inlineStr"/>
       <c r="AV147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>10.1021/i360017a011</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -22465,6 +23200,11 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AU148" t="inlineStr"/>
       <c r="AV148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>10.1021/i360017a011</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -22603,6 +23343,11 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AU149" t="inlineStr"/>
       <c r="AV149" t="inlineStr"/>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>10.1021/i360017a011</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -22741,6 +23486,11 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AU150" t="inlineStr"/>
       <c r="AV150" t="inlineStr"/>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>10.1021/i360017a011</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -22879,6 +23629,11 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AU151" t="inlineStr"/>
       <c r="AV151" t="inlineStr"/>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>10.1021/i360017a011</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -23017,6 +23772,11 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AU152" t="inlineStr"/>
       <c r="AV152" t="inlineStr"/>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>10.1021/i360017a011</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -23155,6 +23915,11 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AU153" t="inlineStr"/>
       <c r="AV153" t="inlineStr"/>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>10.1021/i360017a011</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -23293,6 +24058,11 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AU154" t="inlineStr"/>
       <c r="AV154" t="inlineStr"/>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>10.1021/i360017a011</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -23431,6 +24201,11 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AU155" t="inlineStr"/>
       <c r="AV155" t="inlineStr"/>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>10.1021/i360017a011</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -23575,6 +24350,11 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AU156" t="inlineStr"/>
       <c r="AV156" t="inlineStr"/>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-018-2609-8</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -23719,6 +24499,11 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AU157" t="inlineStr"/>
       <c r="AV157" t="inlineStr"/>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-018-2609-8</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -23863,6 +24648,11 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AU158" t="inlineStr"/>
       <c r="AV158" t="inlineStr"/>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-018-2609-8</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -24007,6 +24797,11 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AU159" t="inlineStr"/>
       <c r="AV159" t="inlineStr"/>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.7b02841</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -24155,6 +24950,11 @@
       <c r="AV160" t="n">
         <v>0.3341511879049677</v>
       </c>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6b03079</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -24309,6 +25109,11 @@
       <c r="AV161" t="n">
         <v>0.006491810919825448</v>
       </c>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.1c04460</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -24457,6 +25262,11 @@
       <c r="AV162" t="n">
         <v>0.1319975760235733</v>
       </c>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>10.1021/acssuschemeng.0c05916</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -24611,6 +25421,11 @@
       <c r="AV163" t="n">
         <v>4.665167584648525</v>
       </c>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-018-2535-9</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -24765,6 +25580,11 @@
       <c r="AV164" t="n">
         <v>9.182349604318869</v>
       </c>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-018-2535-9</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -24913,6 +25733,11 @@
       <c r="AV165" t="n">
         <v>0.2023023758099353</v>
       </c>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6b03079</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -25067,6 +25892,11 @@
       <c r="AV166" t="n">
         <v>14.90164668850127</v>
       </c>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-018-2535-9</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -25221,6 +26051,11 @@
       <c r="AV167" t="n">
         <v>20.23223498611898</v>
       </c>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-018-2535-9</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -25361,6 +26196,11 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AU168" t="inlineStr"/>
       <c r="AV168" t="inlineStr"/>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>10.1109/NAP.2017.8190167</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -25501,6 +26341,11 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AU169" t="inlineStr"/>
       <c r="AV169" t="inlineStr"/>
+      <c r="AW169" t="inlineStr">
+        <is>
+          <t>10.1007/s11144-018-1443-8</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -25641,6 +26486,11 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AU170" t="inlineStr"/>
       <c r="AV170" t="inlineStr"/>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>10.1007/s11144-018-1443-8</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -25781,6 +26631,11 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AU171" t="inlineStr"/>
       <c r="AV171" t="inlineStr"/>
+      <c r="AW171" t="inlineStr">
+        <is>
+          <t>10.1007/s11144-018-1443-8</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -25921,6 +26776,11 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AU172" t="inlineStr"/>
       <c r="AV172" t="inlineStr"/>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t>10.1007/s11144-018-1443-8</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -26069,6 +26929,11 @@
       <c r="AV173" t="n">
         <v>0.8264491835392516</v>
       </c>
+      <c r="AW173" t="inlineStr">
+        <is>
+          <t>10.1016/j.cej.2022.137324</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -26217,6 +27082,11 @@
       <c r="AV174" t="n">
         <v>2.051033978527193</v>
       </c>
+      <c r="AW174" t="inlineStr">
+        <is>
+          <t>10.1016/j.cej.2022.137324</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -26365,6 +27235,11 @@
       <c r="AV175" t="n">
         <v>2.283383057791335</v>
       </c>
+      <c r="AW175" t="inlineStr">
+        <is>
+          <t>10.1016/j.cej.2022.137324</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -26515,6 +27390,11 @@
       <c r="AV176" t="n">
         <v>1.294475002881371</v>
       </c>
+      <c r="AW176" t="inlineStr">
+        <is>
+          <t>10.1016/j.fuel.2023.128414</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -26665,6 +27545,11 @@
       <c r="AV177" t="n">
         <v>1.766123877216917</v>
       </c>
+      <c r="AW177" t="inlineStr">
+        <is>
+          <t>10.1016/j.fuel.2023.128414</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -26815,6 +27700,11 @@
       <c r="AV178" t="n">
         <v>2.891139794209217</v>
       </c>
+      <c r="AW178" t="inlineStr">
+        <is>
+          <t>10.1016/j.fuel.2023.128414</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -26965,6 +27855,11 @@
       <c r="AV179" t="n">
         <v>1.630842938154373</v>
       </c>
+      <c r="AW179" t="inlineStr">
+        <is>
+          <t>10.1039/D2CC06618A</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -27115,6 +28010,11 @@
       <c r="AV180" t="n">
         <v>2.629351562383224</v>
       </c>
+      <c r="AW180" t="inlineStr">
+        <is>
+          <t>10.1039/D2CC06618A</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -27265,6 +28165,11 @@
       <c r="AV181" t="n">
         <v>7.338151450099357</v>
       </c>
+      <c r="AW181" t="inlineStr">
+        <is>
+          <t>10.1039/D2CC06618A</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -27413,6 +28318,11 @@
       <c r="AV182" t="n">
         <v>0.8909859611231106</v>
       </c>
+      <c r="AW182" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6b03079</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -27561,6 +28471,11 @@
       <c r="AV183" t="n">
         <v>0.972259179265659</v>
       </c>
+      <c r="AW183" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6b03079</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -27701,6 +28616,11 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AU184" t="inlineStr"/>
       <c r="AV184" t="inlineStr"/>
+      <c r="AW184" t="inlineStr">
+        <is>
+          <t>10.1007/s11237-020-09658-y</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -27847,6 +28767,11 @@
       <c r="AV185" t="n">
         <v>2.486910633042796</v>
       </c>
+      <c r="AW185" t="inlineStr">
+        <is>
+          <t>10.1016/j.jiec.2016.06.018</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -27993,6 +28918,11 @@
       <c r="AV186" t="n">
         <v>4.218909578452532</v>
       </c>
+      <c r="AW186" t="inlineStr">
+        <is>
+          <t>10.1016/j.jiec.2016.06.018</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -28141,6 +29071,11 @@
       <c r="AV187" t="n">
         <v>1.166689041354884</v>
       </c>
+      <c r="AW187" t="inlineStr">
+        <is>
+          <t>10.1039/D3NJ00221G</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -28289,6 +29224,11 @@
       <c r="AV188" t="n">
         <v>0.8882615471525995</v>
       </c>
+      <c r="AW188" t="inlineStr">
+        <is>
+          <t>10.1038/s41598-019-53180-8</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -28437,6 +29377,11 @@
       <c r="AV189" t="n">
         <v>0.8248099352051836</v>
       </c>
+      <c r="AW189" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6b03079</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -28583,6 +29528,11 @@
       <c r="AV190" t="n">
         <v>0.50102</v>
       </c>
+      <c r="AW190" t="inlineStr">
+        <is>
+          <t>10.1016/0021-9517(87)90285-5</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -28729,6 +29679,11 @@
       <c r="AV191" t="n">
         <v>0.466193</v>
       </c>
+      <c r="AW191" t="inlineStr">
+        <is>
+          <t>10.1016/0021-9517(87)90285-5</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -28875,6 +29830,11 @@
       <c r="AV192" t="n">
         <v>0.1794</v>
       </c>
+      <c r="AW192" t="inlineStr">
+        <is>
+          <t>10.1016/0021-9517(87)90285-5</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -29021,6 +29981,11 @@
       <c r="AV193" t="n">
         <v>0.833</v>
       </c>
+      <c r="AW193" t="inlineStr">
+        <is>
+          <t>10.1016/0021-9517(87)90285-5</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -29167,6 +30132,11 @@
       <c r="AV194" t="n">
         <v>0.7726500000000001</v>
       </c>
+      <c r="AW194" t="inlineStr">
+        <is>
+          <t>10.1016/0021-9517(87)90285-5</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -29313,6 +30283,11 @@
       <c r="AV195" t="n">
         <v>0.2715</v>
       </c>
+      <c r="AW195" t="inlineStr">
+        <is>
+          <t>10.1016/0021-9517(87)90285-5</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -29459,6 +30434,11 @@
       <c r="AV196" t="n">
         <v>0.6375</v>
       </c>
+      <c r="AW196" t="inlineStr">
+        <is>
+          <t>10.1016/0021-9517(87)90285-5</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -29605,6 +30585,11 @@
       <c r="AV197" t="n">
         <v>0.6034999999999999</v>
       </c>
+      <c r="AW197" t="inlineStr">
+        <is>
+          <t>10.1016/0021-9517(87)90285-5</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -29751,6 +30736,11 @@
       <c r="AV198" t="n">
         <v>0.7055</v>
       </c>
+      <c r="AW198" t="inlineStr">
+        <is>
+          <t>10.1016/0021-9517(87)90285-5</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -29897,6 +30887,11 @@
       <c r="AV199" t="n">
         <v>0.374</v>
       </c>
+      <c r="AW199" t="inlineStr">
+        <is>
+          <t>10.1016/0021-9517(87)90285-5</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -30043,6 +31038,11 @@
       <c r="AV200" t="n">
         <v>5.998416666666667</v>
       </c>
+      <c r="AW200" t="inlineStr">
+        <is>
+          <t>10.1016/S0166-9834(00)80265-1</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -30189,6 +31189,11 @@
       <c r="AV201" t="n">
         <v>5.839166666666666</v>
       </c>
+      <c r="AW201" t="inlineStr">
+        <is>
+          <t>10.1016/S0166-9834(00)80265-1</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -30335,6 +31340,11 @@
       <c r="AV202" t="n">
         <v>5.159000000000001</v>
       </c>
+      <c r="AW202" t="inlineStr">
+        <is>
+          <t>10.1016/S0166-9834(00)80265-1</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -30481,6 +31491,11 @@
       <c r="AV203" t="n">
         <v>9.084250000000001</v>
       </c>
+      <c r="AW203" t="inlineStr">
+        <is>
+          <t>10.1016/S0166-9834(00)80265-1</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -30627,6 +31642,11 @@
       <c r="AV204" t="n">
         <v>6.850200000000001</v>
       </c>
+      <c r="AW204" t="inlineStr">
+        <is>
+          <t>10.1016/S0166-9834(00)80265-1</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -30773,6 +31793,11 @@
       <c r="AV205" t="n">
         <v>4.841136363636362</v>
       </c>
+      <c r="AW205" t="inlineStr">
+        <is>
+          <t>10.1016/S0166-9834(00)82351-9</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -30919,6 +31944,11 @@
       <c r="AV206" t="n">
         <v>2.38175</v>
       </c>
+      <c r="AW206" t="inlineStr">
+        <is>
+          <t>10.1016/S0166-9834(00)82351-9</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -31065,6 +32095,11 @@
       <c r="AV207" t="n">
         <v>0.7669374999999999</v>
       </c>
+      <c r="AW207" t="inlineStr">
+        <is>
+          <t>10.1016/S0166-9834(00)82351-9</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -31211,6 +32246,11 @@
       <c r="AV208" t="n">
         <v>6.244318181818182</v>
       </c>
+      <c r="AW208" t="inlineStr">
+        <is>
+          <t>10.1016/S0166-9834(00)82351-9</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -31357,6 +32397,11 @@
       <c r="AV209" t="n">
         <v>3.21895</v>
       </c>
+      <c r="AW209" t="inlineStr">
+        <is>
+          <t>10.1016/S0166-9834(00)82351-9</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -31499,6 +32544,11 @@
         <v>0.4</v>
       </c>
       <c r="AV210" t="inlineStr"/>
+      <c r="AW210" t="inlineStr">
+        <is>
+          <t>10.1016/S0167-2991(08)61662-6</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -31641,6 +32691,11 @@
         <v>0.4</v>
       </c>
       <c r="AV211" t="inlineStr"/>
+      <c r="AW211" t="inlineStr">
+        <is>
+          <t>10.1016/S0167-2991(08)61662-6</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -31783,6 +32838,11 @@
         <v>0.4</v>
       </c>
       <c r="AV212" t="inlineStr"/>
+      <c r="AW212" t="inlineStr">
+        <is>
+          <t>10.1016/S0167-2991(08)61662-6</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -31927,6 +32987,11 @@
         <v>0.4</v>
       </c>
       <c r="AV213" t="inlineStr"/>
+      <c r="AW213" t="inlineStr">
+        <is>
+          <t>10.1016/S0167-2991(08)61662-6</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -32077,6 +33142,11 @@
       <c r="AV214" t="n">
         <v>1.19</v>
       </c>
+      <c r="AW214" t="inlineStr">
+        <is>
+          <t>10.1016/j.jcat.2014.04.005</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -32225,6 +33295,11 @@
       <c r="AV215" t="n">
         <v>1.715683220312576</v>
       </c>
+      <c r="AW215" t="inlineStr">
+        <is>
+          <t>10.1016/j.jcat.2019.04.032</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -32373,6 +33448,11 @@
       <c r="AV216" t="n">
         <v>4.258643622866135</v>
       </c>
+      <c r="AW216" t="inlineStr">
+        <is>
+          <t>10.1016/j.jcat.2019.04.032</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -32521,6 +33601,11 @@
       <c r="AV217" t="n">
         <v>0.7641106978826797</v>
       </c>
+      <c r="AW217" t="inlineStr">
+        <is>
+          <t>10.1016/j.jcat.2019.04.032</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -32669,6 +33754,11 @@
       <c r="AV218" t="n">
         <v>1.114582804644869</v>
       </c>
+      <c r="AW218" t="inlineStr">
+        <is>
+          <t>10.1016/j.jcat.2019.04.032</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -32817,6 +33907,11 @@
       <c r="AV219" t="n">
         <v>1.328533800052019</v>
       </c>
+      <c r="AW219" t="inlineStr">
+        <is>
+          <t>10.1016/j.jcat.2019.04.032</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -32965,6 +34060,11 @@
       <c r="AV220" t="n">
         <v>1.318345657413583</v>
       </c>
+      <c r="AW220" t="inlineStr">
+        <is>
+          <t>10.1016/j.jcat.2019.04.032</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -33113,6 +34213,11 @@
       <c r="AV221" t="n">
         <v>1.428377597908689</v>
       </c>
+      <c r="AW221" t="inlineStr">
+        <is>
+          <t>10.1016/j.jcat.2019.04.032</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -33261,6 +34366,11 @@
       <c r="AV222" t="n">
         <v>1.110507547589495</v>
       </c>
+      <c r="AW222" t="inlineStr">
+        <is>
+          <t>10.1016/j.jcat.2019.04.032</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -33409,6 +34519,11 @@
       <c r="AV223" t="n">
         <v>2.435961924077114</v>
       </c>
+      <c r="AW223" t="inlineStr">
+        <is>
+          <t>10.1039/C9CC08700A</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -33557,6 +34672,11 @@
       <c r="AV224" t="n">
         <v>3.247949232102819</v>
       </c>
+      <c r="AW224" t="inlineStr">
+        <is>
+          <t>10.1039/C9CC08700A</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -33705,6 +34825,11 @@
       <c r="AV225" t="n">
         <v>3.846883326914776</v>
       </c>
+      <c r="AW225" t="inlineStr">
+        <is>
+          <t>10.1039/D2RA06960A</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -33853,6 +34978,11 @@
       <c r="AV226" t="n">
         <v>3.546521561418445</v>
       </c>
+      <c r="AW226" t="inlineStr">
+        <is>
+          <t>10.1039/D2RA06960A</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -34001,6 +35131,11 @@
       <c r="AV227" t="n">
         <v>2.792856697240634</v>
       </c>
+      <c r="AW227" t="inlineStr">
+        <is>
+          <t>10.1039/D2RA06960A</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -34149,6 +35284,11 @@
       <c r="AV228" t="n">
         <v>2.242416016515497</v>
       </c>
+      <c r="AW228" t="inlineStr">
+        <is>
+          <t>10.1039/D2RA06960A</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -34297,6 +35437,11 @@
       <c r="AV229" t="n">
         <v>1.248842148334175</v>
       </c>
+      <c r="AW229" t="inlineStr">
+        <is>
+          <t>10.1039/D3NJ00221G</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -34445,6 +35590,11 @@
       <c r="AV230" t="n">
         <v>1.256074812674627</v>
       </c>
+      <c r="AW230" t="inlineStr">
+        <is>
+          <t>10.1039/D3NJ00221G</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -34592,6 +35742,11 @@
       </c>
       <c r="AV231" t="n">
         <v>1.706493515652707</v>
+      </c>
+      <c r="AW231" t="inlineStr">
+        <is>
+          <t>10.1039/D3NJ00221G</t>
+        </is>
       </c>
     </row>
     <row r="232">
@@ -34731,6 +35886,11 @@
       <c r="AT232" t="inlineStr"/>
       <c r="AU232" t="inlineStr"/>
       <c r="AV232" t="inlineStr"/>
+      <c r="AW232" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.8b02132</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -34869,6 +36029,11 @@
       <c r="AT233" t="inlineStr"/>
       <c r="AU233" t="inlineStr"/>
       <c r="AV233" t="inlineStr"/>
+      <c r="AW233" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.8b02132</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -35007,6 +36172,11 @@
       <c r="AT234" t="inlineStr"/>
       <c r="AU234" t="inlineStr"/>
       <c r="AV234" t="inlineStr"/>
+      <c r="AW234" t="inlineStr">
+        <is>
+          <t>10.1039/C8RA09241A</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -35145,6 +36315,11 @@
       <c r="AT235" t="inlineStr"/>
       <c r="AU235" t="inlineStr"/>
       <c r="AV235" t="inlineStr"/>
+      <c r="AW235" t="inlineStr">
+        <is>
+          <t>10.1039/C8RA09241A</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -35283,6 +36458,11 @@
       <c r="AT236" t="inlineStr"/>
       <c r="AU236" t="inlineStr"/>
       <c r="AV236" t="inlineStr"/>
+      <c r="AW236" t="inlineStr">
+        <is>
+          <t>10.1039/C8RA09241A</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -35421,6 +36601,11 @@
       <c r="AT237" t="inlineStr"/>
       <c r="AU237" t="inlineStr"/>
       <c r="AV237" t="inlineStr"/>
+      <c r="AW237" t="inlineStr">
+        <is>
+          <t>10.1039/C8RA09241A</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -35559,6 +36744,11 @@
       <c r="AT238" t="inlineStr"/>
       <c r="AU238" t="inlineStr"/>
       <c r="AV238" t="inlineStr"/>
+      <c r="AW238" t="inlineStr">
+        <is>
+          <t>10.1039/C8RA09241A</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -35697,6 +36887,11 @@
       <c r="AT239" t="inlineStr"/>
       <c r="AU239" t="inlineStr"/>
       <c r="AV239" t="inlineStr"/>
+      <c r="AW239" t="inlineStr">
+        <is>
+          <t>10.1039/C8RA09241A</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -35845,6 +37040,11 @@
       <c r="AV240" t="n">
         <v>3.757691144708424</v>
       </c>
+      <c r="AW240" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.7b01212</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -35991,6 +37191,11 @@
       <c r="AV241" t="n">
         <v>2.076870410367171</v>
       </c>
+      <c r="AW241" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.7b01212</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -36139,6 +37344,11 @@
       <c r="AV242" t="n">
         <v>5.535637149028079</v>
       </c>
+      <c r="AW242" t="inlineStr">
+        <is>
+          <t>10.1002/ceat.201700500</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -36287,6 +37497,11 @@
       <c r="AV243" t="n">
         <v>1.279067674586033</v>
       </c>
+      <c r="AW243" t="inlineStr">
+        <is>
+          <t>10.1016/j.cattod.2018.06.019</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -36435,6 +37650,11 @@
       <c r="AV244" t="n">
         <v>1.681659467242621</v>
       </c>
+      <c r="AW244" t="inlineStr">
+        <is>
+          <t>10.1016/j.cattod.2018.06.019</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -36583,6 +37803,11 @@
       <c r="AV245" t="n">
         <v>0.774</v>
       </c>
+      <c r="AW245" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.7b03521</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -36731,6 +37956,11 @@
       <c r="AV246" t="n">
         <v>0.7859999999999999</v>
       </c>
+      <c r="AW246" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.7b03521</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -36879,6 +38109,11 @@
       <c r="AV247" t="n">
         <v>0.792</v>
       </c>
+      <c r="AW247" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.7b03521</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -37027,6 +38262,11 @@
       <c r="AV248" t="n">
         <v>0.846</v>
       </c>
+      <c r="AW248" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.7b03521</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -37175,6 +38415,11 @@
       <c r="AV249" t="n">
         <v>0.9059999999999999</v>
       </c>
+      <c r="AW249" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.7b03521</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -37323,6 +38568,11 @@
       <c r="AV250" t="n">
         <v>0.918</v>
       </c>
+      <c r="AW250" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.7b03521</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -37471,6 +38721,11 @@
       <c r="AV251" t="n">
         <v>0.9419999999999999</v>
       </c>
+      <c r="AW251" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.7b03521</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -37619,6 +38874,11 @@
       <c r="AV252" t="n">
         <v>1.014</v>
       </c>
+      <c r="AW252" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.7b03521</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -37767,6 +39027,11 @@
       <c r="AV253" t="n">
         <v>1.044</v>
       </c>
+      <c r="AW253" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.7b03521</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -37915,6 +39180,11 @@
       <c r="AV254" t="n">
         <v>1.116</v>
       </c>
+      <c r="AW254" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.7b03521</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -38055,6 +39325,11 @@
       <c r="AT255" t="inlineStr"/>
       <c r="AU255" t="inlineStr"/>
       <c r="AV255" t="inlineStr"/>
+      <c r="AW255" t="inlineStr">
+        <is>
+          <t>10.1109/NAP.2017.8190167</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -38195,6 +39470,11 @@
       <c r="AT256" t="inlineStr"/>
       <c r="AU256" t="inlineStr"/>
       <c r="AV256" t="inlineStr"/>
+      <c r="AW256" t="inlineStr">
+        <is>
+          <t>10.1109/NAP.2017.8190167</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -38335,6 +39615,11 @@
       <c r="AT257" t="inlineStr"/>
       <c r="AU257" t="inlineStr"/>
       <c r="AV257" t="inlineStr"/>
+      <c r="AW257" t="inlineStr">
+        <is>
+          <t>10.1109/NAP.2017.8190167</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -38473,6 +39758,11 @@
       <c r="AT258" t="inlineStr"/>
       <c r="AU258" t="inlineStr"/>
       <c r="AV258" t="inlineStr"/>
+      <c r="AW258" t="inlineStr">
+        <is>
+          <t>10.1007/s11237-020-09658-y</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -38621,6 +39911,11 @@
       <c r="AV259" t="n">
         <v>0.0452915766738661</v>
       </c>
+      <c r="AW259" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6b03079</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -38769,6 +40064,11 @@
       <c r="AV260" t="n">
         <v>1.092253912062934</v>
       </c>
+      <c r="AW260" t="inlineStr">
+        <is>
+          <t>10.1038/s41598-019-53180-8</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -38915,6 +40215,11 @@
       <c r="AV261" t="n">
         <v>3.275443272788073</v>
       </c>
+      <c r="AW261" t="inlineStr">
+        <is>
+          <t>10.1016/j.jiec.2016.06.018</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -39061,6 +40366,11 @@
       <c r="AV262" t="n">
         <v>5.409777999837072</v>
       </c>
+      <c r="AW262" t="inlineStr">
+        <is>
+          <t>10.1016/j.jiec.2016.06.018</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -39211,6 +40521,11 @@
       <c r="AV263" t="n">
         <v>0.8473623668792444</v>
       </c>
+      <c r="AW263" t="inlineStr">
+        <is>
+          <t>10.1038/s41598-019-53180-8</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -39359,6 +40674,11 @@
       <c r="AV264" t="n">
         <v>1.497223641843269</v>
       </c>
+      <c r="AW264" t="inlineStr">
+        <is>
+          <t>10.1038/s41598-019-53180-8</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -39507,6 +40827,11 @@
       <c r="AV265" t="n">
         <v>1.342631167931669</v>
       </c>
+      <c r="AW265" t="inlineStr">
+        <is>
+          <t>10.1038/s41598-019-53180-8</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -39655,6 +40980,11 @@
       <c r="AV266" t="n">
         <v>3.221065796579677</v>
       </c>
+      <c r="AW266" t="inlineStr">
+        <is>
+          <t>10.1038/s41598-019-53180-8</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -39801,6 +41131,11 @@
         <v>0.3843130724396337</v>
       </c>
       <c r="AV267" t="inlineStr"/>
+      <c r="AW267" t="inlineStr">
+        <is>
+          <t>10.1038/s41598-019-53180-8</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -39949,6 +41284,11 @@
       <c r="AV268" t="n">
         <v>0.6770641338786256</v>
       </c>
+      <c r="AW268" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.5b01422</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -40097,6 +41437,11 @@
       <c r="AV269" t="n">
         <v>0.5234107665098233</v>
       </c>
+      <c r="AW269" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.5b01422</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -40245,6 +41590,11 @@
       <c r="AV270" t="n">
         <v>0.6770641338786256</v>
       </c>
+      <c r="AW270" t="inlineStr">
+        <is>
+          <t>10.1016/j.cej.2016.04.107</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -40393,6 +41743,11 @@
       <c r="AV271" t="n">
         <v>0.9456167857111814</v>
       </c>
+      <c r="AW271" t="inlineStr">
+        <is>
+          <t>10.1016/j.cej.2016.04.107</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -40541,6 +41896,11 @@
       <c r="AV272" t="n">
         <v>0.6542116630669548</v>
       </c>
+      <c r="AW272" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6b03079</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -40681,6 +42041,11 @@
       <c r="AT273" t="inlineStr"/>
       <c r="AU273" t="inlineStr"/>
       <c r="AV273" t="inlineStr"/>
+      <c r="AW273" t="inlineStr">
+        <is>
+          <t>10.15587/1729-4061.2015.37405</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -40821,6 +42186,11 @@
       <c r="AT274" t="inlineStr"/>
       <c r="AU274" t="inlineStr"/>
       <c r="AV274" t="inlineStr"/>
+      <c r="AW274" t="inlineStr">
+        <is>
+          <t>10.1016/j.apcata.2020.117472</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -40961,6 +42331,11 @@
       <c r="AT275" t="inlineStr"/>
       <c r="AU275" t="inlineStr"/>
       <c r="AV275" t="inlineStr"/>
+      <c r="AW275" t="inlineStr">
+        <is>
+          <t>10.1016/j.apcata.2020.117472</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -41101,6 +42476,11 @@
       <c r="AT276" t="inlineStr"/>
       <c r="AU276" t="inlineStr"/>
       <c r="AV276" t="inlineStr"/>
+      <c r="AW276" t="inlineStr">
+        <is>
+          <t>10.1007/s11237-020-09658-y</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -41241,6 +42621,11 @@
       <c r="AT277" t="inlineStr"/>
       <c r="AU277" t="inlineStr"/>
       <c r="AV277" t="inlineStr"/>
+      <c r="AW277" t="inlineStr">
+        <is>
+          <t>10.1007/s11237-020-09658-y</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -41387,6 +42772,11 @@
       <c r="AV278" t="n">
         <v>2.003826076275772</v>
       </c>
+      <c r="AW278" t="inlineStr">
+        <is>
+          <t>10.1016/j.jiec.2016.06.018</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -41533,6 +42923,11 @@
       <c r="AV279" t="n">
         <v>2.893351550265347</v>
       </c>
+      <c r="AW279" t="inlineStr">
+        <is>
+          <t>10.1016/j.jiec.2016.06.018</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -41681,6 +43076,11 @@
       <c r="AV280" t="n">
         <v>7.685634535477528</v>
       </c>
+      <c r="AW280" t="inlineStr">
+        <is>
+          <t>10.1039/C7RA09778F</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -41829,6 +43229,11 @@
       <c r="AV281" t="n">
         <v>10.10657531639547</v>
       </c>
+      <c r="AW281" t="inlineStr">
+        <is>
+          <t>10.1039/C7RA09778F</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -41977,6 +43382,11 @@
       <c r="AV282" t="n">
         <v>10.46241951343293</v>
       </c>
+      <c r="AW282" t="inlineStr">
+        <is>
+          <t>10.1039/C7RA09778F</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -42124,6 +43534,11 @@
       </c>
       <c r="AV283" t="n">
         <v>9.635344308053416</v>
+      </c>
+      <c r="AW283" t="inlineStr">
+        <is>
+          <t>10.1039/C7RA09778F</t>
+        </is>
       </c>
     </row>
     <row r="284">
@@ -42263,6 +43678,11 @@
       <c r="AT284" t="inlineStr"/>
       <c r="AU284" t="inlineStr"/>
       <c r="AV284" t="inlineStr"/>
+      <c r="AW284" t="inlineStr">
+        <is>
+          <t>10.4028/www.scientific.net/AMR.233-235.2859</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -42401,6 +43821,11 @@
       <c r="AT285" t="inlineStr"/>
       <c r="AU285" t="inlineStr"/>
       <c r="AV285" t="inlineStr"/>
+      <c r="AW285" t="inlineStr">
+        <is>
+          <t>10.4028/www.scientific.net/AMR.233-235.2859</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -42549,6 +43974,11 @@
       <c r="AV286" t="n">
         <v>13.68434038301416</v>
       </c>
+      <c r="AW286" t="inlineStr">
+        <is>
+          <t>10.1016/j.apcata.2023.119441</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -42697,6 +44127,11 @@
       <c r="AV287" t="n">
         <v>17.33580195004163</v>
       </c>
+      <c r="AW287" t="inlineStr">
+        <is>
+          <t>10.1016/j.apcata.2023.119441</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -42845,6 +44280,11 @@
       <c r="AV288" t="n">
         <v>17.54505867110741</v>
       </c>
+      <c r="AW288" t="inlineStr">
+        <is>
+          <t>10.1016/j.apcata.2023.119441</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -42993,6 +44433,11 @@
       <c r="AV289" t="n">
         <v>18.07017357202331</v>
       </c>
+      <c r="AW289" t="inlineStr">
+        <is>
+          <t>10.1016/j.apcata.2023.119441</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -43141,6 +44586,11 @@
       <c r="AV290" t="n">
         <v>19.06192839300583</v>
       </c>
+      <c r="AW290" t="inlineStr">
+        <is>
+          <t>10.1016/j.apcata.2023.119441</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -43289,6 +44739,11 @@
       <c r="AV291" t="n">
         <v>2.420641408831346</v>
       </c>
+      <c r="AW291" t="inlineStr">
+        <is>
+          <t>10.1039/C9CC08700A</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -43437,6 +44892,11 @@
       <c r="AV292" t="n">
         <v>2.880256866204387</v>
       </c>
+      <c r="AW292" t="inlineStr">
+        <is>
+          <t>10.1039/C9CC08700A</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -43585,6 +45045,11 @@
       <c r="AV293" t="n">
         <v>3.125385110136675</v>
       </c>
+      <c r="AW293" t="inlineStr">
+        <is>
+          <t>10.1039/C9CC08700A</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -43733,6 +45198,11 @@
       <c r="AV294" t="n">
         <v>3.033462018662067</v>
       </c>
+      <c r="AW294" t="inlineStr">
+        <is>
+          <t>10.1039/C9CC08700A</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -43873,6 +45343,11 @@
       <c r="AT295" t="inlineStr"/>
       <c r="AU295" t="inlineStr"/>
       <c r="AV295" t="inlineStr"/>
+      <c r="AW295" t="inlineStr">
+        <is>
+          <t>10.1007/s11237-020-09658-y</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -44021,6 +45496,11 @@
       <c r="AV296" t="n">
         <v>1.01056186830644</v>
       </c>
+      <c r="AW296" t="inlineStr">
+        <is>
+          <t>10.1021/acssuschemeng.0c05916</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -44169,6 +45649,11 @@
       <c r="AV297" t="n">
         <v>1.450154752798345</v>
       </c>
+      <c r="AW297" t="inlineStr">
+        <is>
+          <t>10.1021/acssuschemeng.0c05916</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -44317,6 +45802,11 @@
       <c r="AV298" t="n">
         <v>0.6014824710166493</v>
       </c>
+      <c r="AW298" t="inlineStr">
+        <is>
+          <t>10.1021/acssuschemeng.0c05916</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -44465,6 +45955,11 @@
       <c r="AV299" t="n">
         <v>0.6327753511306047</v>
       </c>
+      <c r="AW299" t="inlineStr">
+        <is>
+          <t>10.1021/acssuschemeng.0c05916</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -44613,6 +46108,11 @@
       <c r="AV300" t="n">
         <v>0.4906587473002161</v>
       </c>
+      <c r="AW300" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6b03079</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -44753,6 +46253,11 @@
       <c r="AT301" t="inlineStr"/>
       <c r="AU301" t="inlineStr"/>
       <c r="AV301" t="inlineStr"/>
+      <c r="AW301" t="inlineStr">
+        <is>
+          <t>10.1007/s11237-020-09658-y</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -44903,6 +46408,11 @@
       <c r="AV302" t="n">
         <v>7.869421565362199</v>
       </c>
+      <c r="AW302" t="inlineStr">
+        <is>
+          <t>10.19906/j.cnki.JFCT.2022036</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -45051,6 +46561,11 @@
       <c r="AV303" t="n">
         <v>0.4977041036717064</v>
       </c>
+      <c r="AW303" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6b03079</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -45199,6 +46714,11 @@
       <c r="AV304" t="n">
         <v>4.775040441526312</v>
       </c>
+      <c r="AW304" t="inlineStr">
+        <is>
+          <t>10.1002/jctb.6360</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -45339,6 +46859,11 @@
       <c r="AT305" t="inlineStr"/>
       <c r="AU305" t="inlineStr"/>
       <c r="AV305" t="inlineStr"/>
+      <c r="AW305" t="inlineStr">
+        <is>
+          <t>10.15587/1729-4061.2013.19130</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -45487,6 +47012,11 @@
       <c r="AV306" t="n">
         <v>5.648172043010754</v>
       </c>
+      <c r="AW306" t="inlineStr">
+        <is>
+          <t>10.1002/jctb.6360</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -45635,6 +47165,11 @@
       <c r="AV307" t="n">
         <v>0.2511166306695465</v>
       </c>
+      <c r="AW307" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6b03079</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -45783,6 +47318,11 @@
       <c r="AV308" t="n">
         <v>1.212167332354212</v>
       </c>
+      <c r="AW308" t="inlineStr">
+        <is>
+          <t>10.1002/cjce.22889</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -45931,6 +47471,11 @@
       <c r="AV309" t="n">
         <v>0.9152924607343416</v>
       </c>
+      <c r="AW309" t="inlineStr">
+        <is>
+          <t>10.1002/cjce.22889</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -46079,6 +47624,11 @@
       <c r="AV310" t="n">
         <v>1.209156348336933</v>
       </c>
+      <c r="AW310" t="inlineStr">
+        <is>
+          <t>10.1002/cjce.22889</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -46225,6 +47775,11 @@
       <c r="AV311" t="n">
         <v>0.7289173602215658</v>
       </c>
+      <c r="AW311" t="inlineStr">
+        <is>
+          <t>10.1016/j.micromeso.2017.07.045</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -46371,6 +47926,11 @@
       <c r="AV312" t="n">
         <v>0.7658212206013317</v>
       </c>
+      <c r="AW312" t="inlineStr">
+        <is>
+          <t>10.1016/j.micromeso.2017.07.045</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -46517,6 +48077,11 @@
       <c r="AV313" t="n">
         <v>0.9793687450907784</v>
       </c>
+      <c r="AW313" t="inlineStr">
+        <is>
+          <t>10.1016/j.micromeso.2017.07.045</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -46665,6 +48230,11 @@
       <c r="AV314" t="n">
         <v>1.298358531317495</v>
       </c>
+      <c r="AW314" t="inlineStr">
+        <is>
+          <t>10.1016/j.micromeso.2017.07.045</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -46812,6 +48382,11 @@
       </c>
       <c r="AV315" t="n">
         <v>1.093485388871236</v>
+      </c>
+      <c r="AW315" t="inlineStr">
+        <is>
+          <t>10.1016/j.micromeso.2017.07.045</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/data_clean.xlsx
+++ b/data/data_clean.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/73d4a18d9c9284b4/KULeuven/Ac2Gen/preDissemination/Acetate-Acrylate_review/ML_Literature/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_5EF5D0B7D320D16E5FF93111595ED87656C52FEA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_5EF5D0B7D320D16E5FF93111595ED87656C52FEA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{575ECCE8-02EC-470F-979D-216DCEF909C2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -793,6 +793,53 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AW315"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="3.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="2.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="2.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="3.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="2.140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="3.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="3.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="2.5703125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="3.140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="2.7109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="3.140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="2.5703125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="2.28515625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="3" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="3.140625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="2.7109375" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="12" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="12" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="43.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
